--- a/CDE_ID_detective_revamp/in/Testfile.xlsx
+++ b/CDE_ID_detective_revamp/in/Testfile.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lmaefos\Code Stuffs\CDE_detective\CDE_ID_detective_revamp\in\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lmaefos\Documents\HEAL-Related Documents\Common Data Elements\CDEs Utilization Report\Input from CDE-ID\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B0DA9DF-E808-4D3D-95C8-F209EC06358E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{591629B9-32DF-4DD8-B7AB-0499EDDA7EED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-36930" yWindow="7935" windowWidth="28800" windowHeight="15105" xr2:uid="{B4172F7E-1829-43FF-A6F3-7109D1C548C2}"/>
+    <workbookView xWindow="-36210" yWindow="10035" windowWidth="28800" windowHeight="15105" xr2:uid="{B4172F7E-1829-43FF-A6F3-7109D1C548C2}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="395" uniqueCount="191">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1289" uniqueCount="465">
   <si>
     <t>schemaVersion</t>
   </si>
@@ -143,9 +143,6 @@
     <t>subjectid</t>
   </si>
   <si>
-    <t>OBOE Study Number</t>
-  </si>
-  <si>
     <t>oboe_group</t>
   </si>
   <si>
@@ -606,6 +603,831 @@
   </si>
   <si>
     <t>SECTION A. EMERGENCY ROOM/ACUTE CARE CENTER VISITS: 1st time[choice=Diarrhea]</t>
+  </si>
+  <si>
+    <t>bpiint</t>
+  </si>
+  <si>
+    <t>BPIPainIntfrGnrlActvtyScl</t>
+  </si>
+  <si>
+    <t>General Activity</t>
+  </si>
+  <si>
+    <t>0|1|2|3|4|5|6|7|8|9|10</t>
+  </si>
+  <si>
+    <t>0=Does not interfere (0)|1=1|2=2|3=3|4=4|5=5|6=6|7=7|8=8|9=9|10=Completely interferes (10)</t>
+  </si>
+  <si>
+    <t>BPIPainIntfrMoodScl</t>
+  </si>
+  <si>
+    <t>Mood</t>
+  </si>
+  <si>
+    <t>BPIPainIntfrWlkAblScl</t>
+  </si>
+  <si>
+    <t>Walking Ability</t>
+  </si>
+  <si>
+    <t>BPIPainNrmlWrkIntrfrScl</t>
+  </si>
+  <si>
+    <t>Normal Work</t>
+  </si>
+  <si>
+    <t>BPIPainRelationsIntrfrScl</t>
+  </si>
+  <si>
+    <t>Relations with Other People</t>
+  </si>
+  <si>
+    <t>BPIPainSleepIntrfrScl</t>
+  </si>
+  <si>
+    <t>Sleep</t>
+  </si>
+  <si>
+    <t>BPIPainEnjoymntIntrfrScl</t>
+  </si>
+  <si>
+    <t>Enjoyment of Life</t>
+  </si>
+  <si>
+    <t>bpisev</t>
+  </si>
+  <si>
+    <t>BPIWrstPnLast24HRtngScl</t>
+  </si>
+  <si>
+    <t>Worst Pain in the Last 24 Hours</t>
+  </si>
+  <si>
+    <t>0=No pain (0)|1=1|2=2|3=3|4=4|5=5|6=6|7=7|8=8|9=9|10=Pain as bad as you can imagine (10)</t>
+  </si>
+  <si>
+    <t>BPILeastPnLst24HRtngScl</t>
+  </si>
+  <si>
+    <t>Least Pain in the Last 24 Hours</t>
+  </si>
+  <si>
+    <t>BPIAvgPainRtngScl</t>
+  </si>
+  <si>
+    <t>Average Pain</t>
+  </si>
+  <si>
+    <t>BPICurrentPainRtngScl</t>
+  </si>
+  <si>
+    <t>Current Pain</t>
+  </si>
+  <si>
+    <t>gad7</t>
+  </si>
+  <si>
+    <t>GAD2FeelNervScl</t>
+  </si>
+  <si>
+    <t>Feeling Nervous</t>
+  </si>
+  <si>
+    <t>0|1|2|3</t>
+  </si>
+  <si>
+    <t>0=Not at all|1=Several Days|2=More than half the days|3=Nearly every day</t>
+  </si>
+  <si>
+    <t>GAD2NotStopWryScl</t>
+  </si>
+  <si>
+    <t>Unable to Stop Worrying</t>
+  </si>
+  <si>
+    <t>GAD7WryTooMchScl</t>
+  </si>
+  <si>
+    <t>Worrying Too Much</t>
+  </si>
+  <si>
+    <t>GAD7TroubRelxScl</t>
+  </si>
+  <si>
+    <t>Trouble Relaxing</t>
+  </si>
+  <si>
+    <t>GAD7RstlessScl</t>
+  </si>
+  <si>
+    <t>Being Restless</t>
+  </si>
+  <si>
+    <t>GAD7EasyAnnoyedScl</t>
+  </si>
+  <si>
+    <t>Becoming Easily Annoyed/Irritable</t>
+  </si>
+  <si>
+    <t>GAD7FeelAfrdScl</t>
+  </si>
+  <si>
+    <t>Feeling Afraid</t>
+  </si>
+  <si>
+    <t>pcs6</t>
+  </si>
+  <si>
+    <t>PCQPainAwfulOvrwhlmScl</t>
+  </si>
+  <si>
+    <t>Awful and Overwhelming</t>
+  </si>
+  <si>
+    <t>0|1|2|3|4</t>
+  </si>
+  <si>
+    <t>0=Not at all|1=To a slight degree|2=To a moderate degree|3=To a great degree|4=All the time</t>
+  </si>
+  <si>
+    <t>PCQFeelCantWithstandScl</t>
+  </si>
+  <si>
+    <t>Can't Stand it Anymore</t>
+  </si>
+  <si>
+    <t>PCQAfraidPainWorseScl</t>
+  </si>
+  <si>
+    <t>Afraid it Will Get Worse</t>
+  </si>
+  <si>
+    <t>PCQHurtScl</t>
+  </si>
+  <si>
+    <t>Thinks about How Much it Hurts</t>
+  </si>
+  <si>
+    <t>PCQPainStopScl</t>
+  </si>
+  <si>
+    <t>Badly Wants it to Stop</t>
+  </si>
+  <si>
+    <t>PCQSeriousScl</t>
+  </si>
+  <si>
+    <t>Wonders whether Something Serious Will Happen</t>
+  </si>
+  <si>
+    <t>pcsd</t>
+  </si>
+  <si>
+    <t>pcst1</t>
+  </si>
+  <si>
+    <t>Permanently Stopped PCST</t>
+  </si>
+  <si>
+    <t>0=No|1=Yes</t>
+  </si>
+  <si>
+    <t>pcst2</t>
+  </si>
+  <si>
+    <t>Reason for Permanently Stopping PCST</t>
+  </si>
+  <si>
+    <t>1|2|3|4|5|6</t>
+  </si>
+  <si>
+    <t>1=Participant does not find PCST helpful|2=Medical condition/event|3=Participant experienced negative event related to PCST|4=Participant finds PCST too burdensome|5=Change in life circumstance|6=Other (Please Specify)</t>
+  </si>
+  <si>
+    <t>pcst2otr</t>
+  </si>
+  <si>
+    <t>Other Reason for Permanently Stopping PCST</t>
+  </si>
+  <si>
+    <t>pcst3</t>
+  </si>
+  <si>
+    <t>Person Driving the Decision to Permanently Stop</t>
+  </si>
+  <si>
+    <t>1|2|3|4</t>
+  </si>
+  <si>
+    <t>1=Investigator's decision|2=PCST coach's decision|3=Participant's decision|4=Participant's usual care clinician</t>
+  </si>
+  <si>
+    <t>pcst_stop_week</t>
+  </si>
+  <si>
+    <t>Study week when PCST permanently stopped</t>
+  </si>
+  <si>
+    <t>pcst6</t>
+  </si>
+  <si>
+    <t>Willing to Continue Participating</t>
+  </si>
+  <si>
+    <t>pcst_level</t>
+  </si>
+  <si>
+    <t>ind_pcst_session_expected</t>
+  </si>
+  <si>
+    <t>PCST Session Expected Pain Interference Scorable</t>
+  </si>
+  <si>
+    <t>pcst_coach_initials_code</t>
+  </si>
+  <si>
+    <t>PCST Coach Initials</t>
+  </si>
+  <si>
+    <t>1=CC|2=HH|3=KP|4=VD|5=BC|6=EK</t>
+  </si>
+  <si>
+    <t>pcst_coach_name</t>
+  </si>
+  <si>
+    <t>PCST Coach Name</t>
+  </si>
+  <si>
+    <t>pcst_completed_weekday</t>
+  </si>
+  <si>
+    <t>Weekday PCST Session Completed</t>
+  </si>
+  <si>
+    <t>pcst_days</t>
+  </si>
+  <si>
+    <t>Days Between Randomization and PCST session</t>
+  </si>
+  <si>
+    <t>pcst_started_hour_eastern</t>
+  </si>
+  <si>
+    <t>Hour PCST Session Started (EST)</t>
+  </si>
+  <si>
+    <t>pcst_started_hourminute_eastern</t>
+  </si>
+  <si>
+    <t>Hour-Minute PCST Session Started (EST)</t>
+  </si>
+  <si>
+    <t>pcstcont_5_other_cat</t>
+  </si>
+  <si>
+    <t>Other Location Where PCST Session was Completed</t>
+  </si>
+  <si>
+    <t>1|2|3|4|5|6|7|8|9|10|11</t>
+  </si>
+  <si>
+    <t>1=Doctor's office|2=Hospital|3=Hotel|4=Nursing home|5=Park|6=Rehab facility|7=SNF|8=Teleconferencing|9=Vehicle|10=While visiting others|11=While walking</t>
+  </si>
+  <si>
+    <t>pcstcont</t>
+  </si>
+  <si>
+    <t>pcstcont_1</t>
+  </si>
+  <si>
+    <t>PCST Session Number</t>
+  </si>
+  <si>
+    <t>1|2|3|4|5|6|7|8|9|10|11|12</t>
+  </si>
+  <si>
+    <t>1=PCST session 1|2=PCST session 2|3=PCST session 3|4=PCST session 4|5=PCST session 5|6=PCST session 6|7=PCST session 7|8=PCST session 8|9=PCST session 9|10=PCST session 10|11=PCST session 11|12=PCST session 12</t>
+  </si>
+  <si>
+    <t>pcstcont_3</t>
+  </si>
+  <si>
+    <t>PCST Session Completed</t>
+  </si>
+  <si>
+    <t>pcstcont_3c</t>
+  </si>
+  <si>
+    <t>Duration of Session</t>
+  </si>
+  <si>
+    <t>pcstcont_3f</t>
+  </si>
+  <si>
+    <t>Session Recorded</t>
+  </si>
+  <si>
+    <t>pcstcont_3g</t>
+  </si>
+  <si>
+    <t>Reason Session Not Recorded</t>
+  </si>
+  <si>
+    <t>1=Recording not permitted|2=Patient preference|3=Technical difficulties|4=Other (specify)</t>
+  </si>
+  <si>
+    <t>pcstcont_3h</t>
+  </si>
+  <si>
+    <t>Reason Session Not Completed</t>
+  </si>
+  <si>
+    <t>1|2|3|4|5|6|7|8|9</t>
+  </si>
+  <si>
+    <t>1=Patient hospitalized|2=Patient on vacation|3=Unable to contact|4=Technical difficulties|5=Life circumstances/stressors|6=Participant was uncomfortable during prior session and does not wish to complete session|7=Other (specify)|8=RC unavailable to facilitate|9=Participant not feeling well</t>
+  </si>
+  <si>
+    <t>pcstcont_3i</t>
+  </si>
+  <si>
+    <t>Session Rescheduled</t>
+  </si>
+  <si>
+    <t>0|1|99</t>
+  </si>
+  <si>
+    <t>0=No|1=Yes|99=N/A</t>
+  </si>
+  <si>
+    <t>pcstcont_3j</t>
+  </si>
+  <si>
+    <t>Information about Last Missed Session Updated</t>
+  </si>
+  <si>
+    <t>pcstcont_4</t>
+  </si>
+  <si>
+    <t>Implementation Method</t>
+  </si>
+  <si>
+    <t>1=Video|2=Telephone</t>
+  </si>
+  <si>
+    <t>pcstcont_5</t>
+  </si>
+  <si>
+    <t>Location of Participant During Session</t>
+  </si>
+  <si>
+    <t>1|2|3</t>
+  </si>
+  <si>
+    <t>1=Dialysis unit|2=Home|3=Other (please specify)</t>
+  </si>
+  <si>
+    <t>pcstcont_6a</t>
+  </si>
+  <si>
+    <t>Agenda/Homework Review Completed</t>
+  </si>
+  <si>
+    <t>pcstcont_6b</t>
+  </si>
+  <si>
+    <t>Key Content Completed</t>
+  </si>
+  <si>
+    <t>pcstcont_6c</t>
+  </si>
+  <si>
+    <t>Experiential Practice Completed</t>
+  </si>
+  <si>
+    <t>pcstcont_6d</t>
+  </si>
+  <si>
+    <t>Weekly MI Goal Completed</t>
+  </si>
+  <si>
+    <t>pcstcont_6e</t>
+  </si>
+  <si>
+    <t>Homework Assigned</t>
+  </si>
+  <si>
+    <t>pcstcont_7</t>
+  </si>
+  <si>
+    <t>Session Disrupted</t>
+  </si>
+  <si>
+    <t>pcstcont_7a</t>
+  </si>
+  <si>
+    <t>Reason Session Disrupted</t>
+  </si>
+  <si>
+    <t>pcstcont_8</t>
+  </si>
+  <si>
+    <t>Homework Completed</t>
+  </si>
+  <si>
+    <t>pcstcont_9</t>
+  </si>
+  <si>
+    <t>Participant's Level of Engagement</t>
+  </si>
+  <si>
+    <t>1|2|3|4|5|6|7|8|9|10</t>
+  </si>
+  <si>
+    <t>1=1 (Not Engaged)|2=2|3=3|4=4|5=5|6=6|7=7|8=8|9=9|10=10 (Very Engaged)</t>
+  </si>
+  <si>
+    <t>pcstcont_10</t>
+  </si>
+  <si>
+    <t>Participant Receiving Support from Other Sources</t>
+  </si>
+  <si>
+    <t>1=Other therapist|2=Religious leader|3=Other (please specify)</t>
+  </si>
+  <si>
+    <t>pcstcont_12</t>
+  </si>
+  <si>
+    <t>Next Session Scheduled</t>
+  </si>
+  <si>
+    <t>pcstcont_12b</t>
+  </si>
+  <si>
+    <t>Participant's Earliest Preferred Contact Time</t>
+  </si>
+  <si>
+    <t>datetime</t>
+  </si>
+  <si>
+    <t>pcstcont_12b_2</t>
+  </si>
+  <si>
+    <t>Participant's Latest Preferred Contact Time</t>
+  </si>
+  <si>
+    <t>pcstcont_13</t>
+  </si>
+  <si>
+    <t>Participant Enrolled into IVR</t>
+  </si>
+  <si>
+    <t>pcstcont_14</t>
+  </si>
+  <si>
+    <t>Participant Confirmed for IVR</t>
+  </si>
+  <si>
+    <t>pcstcont_15</t>
+  </si>
+  <si>
+    <t>Make-up Session</t>
+  </si>
+  <si>
+    <t>pcstcont_16</t>
+  </si>
+  <si>
+    <t>Session Completed over Multiple Days</t>
+  </si>
+  <si>
+    <t>pcstcont_16a</t>
+  </si>
+  <si>
+    <t>Number of Days</t>
+  </si>
+  <si>
+    <t>peg</t>
+  </si>
+  <si>
+    <t>peg1</t>
+  </si>
+  <si>
+    <t>0=0|1=1|2=2|3=3|4=4|5=5|6=6|7=7|8=8|9=9|10=10</t>
+  </si>
+  <si>
+    <t>peg2</t>
+  </si>
+  <si>
+    <t>Pain Interference with Enjoyment of Life</t>
+  </si>
+  <si>
+    <t>peg3</t>
+  </si>
+  <si>
+    <t>Pain Interference with General Activity</t>
+  </si>
+  <si>
+    <t>pegscr1</t>
+  </si>
+  <si>
+    <t>PEG Score</t>
+  </si>
+  <si>
+    <t>pegscr2</t>
+  </si>
+  <si>
+    <t>Derived PEG Score</t>
+  </si>
+  <si>
+    <t>pgic</t>
+  </si>
+  <si>
+    <t>pgic_1</t>
+  </si>
+  <si>
+    <t>Pain Since Start of Study</t>
+  </si>
+  <si>
+    <t>0|1|2|3|4|5|6</t>
+  </si>
+  <si>
+    <t>0=Very much improved|1=Much improved|2=Minimally improved|3=No Change|4=Minimally worse|5=Much worse|6=Very much worse</t>
+  </si>
+  <si>
+    <t>phq9</t>
+  </si>
+  <si>
+    <t>PHQBttrDdThghtScore</t>
+  </si>
+  <si>
+    <t>Frequency of Thoughts of Self Harm or Being Better Off Dead</t>
+  </si>
+  <si>
+    <t>0=Not at all|1=Several days|2=More than half the days|3=Nearly every day</t>
+  </si>
+  <si>
+    <t>PHQBttrDdThghtScore_1a</t>
+  </si>
+  <si>
+    <t>Wished to be Dead in the Past Month</t>
+  </si>
+  <si>
+    <t>PHQBttrDdThghtScore_1b</t>
+  </si>
+  <si>
+    <t>Suicidal Thoughts in the Past Month</t>
+  </si>
+  <si>
+    <t>PHQLitIntrstScore</t>
+  </si>
+  <si>
+    <t>Little Interest or Pleasure in Doing Things</t>
+  </si>
+  <si>
+    <t>PHQDeprssnScore</t>
+  </si>
+  <si>
+    <t>Feeling Down, Depressed, or Hopeless</t>
+  </si>
+  <si>
+    <t>PHQSleepImpairScore</t>
+  </si>
+  <si>
+    <t>Trouble Falling or Staying Asleep, or Sleeping Too Much</t>
+  </si>
+  <si>
+    <t>PHQTirdLittleEnrgyScore</t>
+  </si>
+  <si>
+    <t>Feeling Tired or Having Little Energy</t>
+  </si>
+  <si>
+    <t>PHQAbnrmlDietScore</t>
+  </si>
+  <si>
+    <t>Poor Appetite or Overeating</t>
+  </si>
+  <si>
+    <t>PHQFlngFailrScore</t>
+  </si>
+  <si>
+    <t>Feeling Bad about Yourself</t>
+  </si>
+  <si>
+    <t>PHQConcntrtnImprmntScore</t>
+  </si>
+  <si>
+    <t>Trouble Concentrating</t>
+  </si>
+  <si>
+    <t>PHQMovmntSpchImprmntScore</t>
+  </si>
+  <si>
+    <t>Moving/Speaking Slowly or Feeling Fidgety/Restless</t>
+  </si>
+  <si>
+    <t>PHQDiffcltyPerfScl</t>
+  </si>
+  <si>
+    <t>Difficulty of Work/Housework/Relationships</t>
+  </si>
+  <si>
+    <t>0=Not difficult at all|1=Somewhat difficult|2=Very difficult|3=Extremely difficult</t>
+  </si>
+  <si>
+    <t>taps</t>
+  </si>
+  <si>
+    <t>tap11</t>
+  </si>
+  <si>
+    <t>Frequency of &gt;= 5 Drinks Per Day (Males Only)</t>
+  </si>
+  <si>
+    <t>0=Daily or almost daily|1=Weekly|2=Monthly|3=Less than monthly|4=Never</t>
+  </si>
+  <si>
+    <t>tap12</t>
+  </si>
+  <si>
+    <t>Frequency of &gt;= 4 Drinks Per Day (Females Only)</t>
+  </si>
+  <si>
+    <t>tap13</t>
+  </si>
+  <si>
+    <t>Frequency of Drug Use</t>
+  </si>
+  <si>
+    <t>tap14</t>
+  </si>
+  <si>
+    <t>Frequency of Prescription Medication Use</t>
+  </si>
+  <si>
+    <t>tap21</t>
+  </si>
+  <si>
+    <t>Recent Alcohol Use</t>
+  </si>
+  <si>
+    <t>tap2_11</t>
+  </si>
+  <si>
+    <t>&gt;= 4 Drinks Per Day in the Past 3 Months (Females Only)</t>
+  </si>
+  <si>
+    <t>tap2_12</t>
+  </si>
+  <si>
+    <t>&gt;= 5 Drinks Per Day in the Past 3 Months (Males Only)</t>
+  </si>
+  <si>
+    <t>tap2_13</t>
+  </si>
+  <si>
+    <t>Tried and Failed to Control, Cut Down, or Stop Drinking</t>
+  </si>
+  <si>
+    <t>tap2_14</t>
+  </si>
+  <si>
+    <t>Others Expressed Concern about Participant's Drinking</t>
+  </si>
+  <si>
+    <t>tap22</t>
+  </si>
+  <si>
+    <t>Recent Marijuana Use</t>
+  </si>
+  <si>
+    <t>tap2_21</t>
+  </si>
+  <si>
+    <t>Strong Desire/Urge to Use Marijuana at Least Once a Week</t>
+  </si>
+  <si>
+    <t>tap2_22</t>
+  </si>
+  <si>
+    <t>Others Expressed Concern about Participant's Marijuana Use</t>
+  </si>
+  <si>
+    <t>tap23</t>
+  </si>
+  <si>
+    <t>Recent Cocaine, Crack, or Meth Use</t>
+  </si>
+  <si>
+    <t>tap2_31</t>
+  </si>
+  <si>
+    <t>Cocaine, Crack, or Meth Use at Least Once a Week</t>
+  </si>
+  <si>
+    <t>tap2_32</t>
+  </si>
+  <si>
+    <t>Others Expressed Concern about Participant's Cocaine/Crack/Meth Use</t>
+  </si>
+  <si>
+    <t>tap24</t>
+  </si>
+  <si>
+    <t>Recent Heroin Use</t>
+  </si>
+  <si>
+    <t>tap2_41</t>
+  </si>
+  <si>
+    <t>Tried and Failed to Control, Cut Down, or Stop Using Heroin</t>
+  </si>
+  <si>
+    <t>tap2_42</t>
+  </si>
+  <si>
+    <t>Others Expressed Concern about Participant's Heroin Use</t>
+  </si>
+  <si>
+    <t>tap25</t>
+  </si>
+  <si>
+    <t>Recent Unprescribed Prescription Opiate Pain Reliever Use</t>
+  </si>
+  <si>
+    <t>tap2_51</t>
+  </si>
+  <si>
+    <t>Tried and Failed to Control, Cut Down, or Stop Using Unprescribed Opiate Pain Relievers</t>
+  </si>
+  <si>
+    <t>tap2_52</t>
+  </si>
+  <si>
+    <t>Others Expressed Concern about Participant's Unprescribed Prescription Opiate Pain Reliever Use</t>
+  </si>
+  <si>
+    <t>tap26</t>
+  </si>
+  <si>
+    <t>Recent Unprescribed Anxiety/Sleep Medication Use</t>
+  </si>
+  <si>
+    <t>tap2_61</t>
+  </si>
+  <si>
+    <t>Strong Desire/Urge to Use Anxiety/Sleep Medications at Least Once a Week</t>
+  </si>
+  <si>
+    <t>tap2_62</t>
+  </si>
+  <si>
+    <t>Others Expressed Concern about Participant's Anxiety/Sleep Medication Use</t>
+  </si>
+  <si>
+    <t>tap27</t>
+  </si>
+  <si>
+    <t>Recent Unprescribed ADHD Medication Use</t>
+  </si>
+  <si>
+    <t>tap2_71</t>
+  </si>
+  <si>
+    <t>Unprescribed ADHD Medication Use at Least Once a Week</t>
+  </si>
+  <si>
+    <t>tap2_72</t>
+  </si>
+  <si>
+    <t>Others Expressed Concern about Participant's ADHD Medication Use</t>
+  </si>
+  <si>
+    <t>tap28</t>
+  </si>
+  <si>
+    <t>Other Recent Illegal/Recreational Drug Use</t>
+  </si>
+  <si>
+    <t>tap2_8a1</t>
+  </si>
+  <si>
+    <t>Other Illegal/Recreational Drug</t>
+  </si>
+  <si>
+    <t>tap2_8a2</t>
+  </si>
+  <si>
+    <t>tap2_8a3</t>
+  </si>
+  <si>
+    <t>tap2_8a4</t>
+  </si>
+  <si>
+    <t>Study Number</t>
   </si>
 </sst>
 </file>
@@ -1466,8 +2288,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B4F619F0-927D-42BE-B802-34E76A1D5A02}">
-  <dimension ref="A1:AD52"/>
+  <dimension ref="A1:AD168"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <cols>
+    <col min="2" max="2" width="33.19921875" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:30" x14ac:dyDescent="0.45">
       <c r="A1" t="s">
@@ -1592,10 +2417,10 @@
         <v>35</v>
       </c>
       <c r="D3" t="s">
-        <v>36</v>
+        <v>464</v>
       </c>
       <c r="E3" t="s">
-        <v>36</v>
+        <v>464</v>
       </c>
       <c r="F3" t="s">
         <v>34</v>
@@ -1609,22 +2434,22 @@
         <v>31</v>
       </c>
       <c r="C4" t="s">
+        <v>36</v>
+      </c>
+      <c r="D4" t="s">
         <v>37</v>
       </c>
-      <c r="D4" t="s">
-        <v>38</v>
-      </c>
       <c r="E4" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F4" t="s">
+        <v>38</v>
+      </c>
+      <c r="J4" t="s">
         <v>39</v>
       </c>
-      <c r="J4" t="s">
+      <c r="N4" t="s">
         <v>40</v>
-      </c>
-      <c r="N4" t="s">
-        <v>41</v>
       </c>
     </row>
     <row r="5" spans="1:30" x14ac:dyDescent="0.45">
@@ -1635,16 +2460,16 @@
         <v>31</v>
       </c>
       <c r="C5" t="s">
+        <v>41</v>
+      </c>
+      <c r="D5" t="s">
         <v>42</v>
       </c>
-      <c r="D5" t="s">
+      <c r="E5" t="s">
         <v>43</v>
       </c>
-      <c r="E5" t="s">
+      <c r="F5" t="s">
         <v>44</v>
-      </c>
-      <c r="F5" t="s">
-        <v>45</v>
       </c>
     </row>
     <row r="6" spans="1:30" x14ac:dyDescent="0.45">
@@ -1655,19 +2480,19 @@
         <v>31</v>
       </c>
       <c r="C6" t="s">
+        <v>45</v>
+      </c>
+      <c r="D6" t="s">
         <v>46</v>
       </c>
-      <c r="D6" t="s">
+      <c r="E6" t="s">
+        <v>46</v>
+      </c>
+      <c r="F6" t="s">
         <v>47</v>
       </c>
-      <c r="E6" t="s">
-        <v>47</v>
-      </c>
-      <c r="F6" t="s">
+      <c r="G6" t="s">
         <v>48</v>
-      </c>
-      <c r="G6" t="s">
-        <v>49</v>
       </c>
     </row>
     <row r="7" spans="1:30" x14ac:dyDescent="0.45">
@@ -1678,13 +2503,13 @@
         <v>31</v>
       </c>
       <c r="C7" t="s">
+        <v>49</v>
+      </c>
+      <c r="D7" t="s">
         <v>50</v>
       </c>
-      <c r="D7" t="s">
-        <v>51</v>
-      </c>
       <c r="E7" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="F7" t="s">
         <v>34</v>
@@ -1698,13 +2523,13 @@
         <v>31</v>
       </c>
       <c r="C8" t="s">
+        <v>51</v>
+      </c>
+      <c r="D8" t="s">
         <v>52</v>
       </c>
-      <c r="D8" t="s">
-        <v>53</v>
-      </c>
       <c r="E8" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F8" t="s">
         <v>34</v>
@@ -1718,13 +2543,13 @@
         <v>31</v>
       </c>
       <c r="C9" t="s">
+        <v>53</v>
+      </c>
+      <c r="D9" t="s">
         <v>54</v>
       </c>
-      <c r="D9" t="s">
-        <v>55</v>
-      </c>
       <c r="E9" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F9" t="s">
         <v>34</v>
@@ -1738,22 +2563,22 @@
         <v>31</v>
       </c>
       <c r="C10" t="s">
+        <v>55</v>
+      </c>
+      <c r="D10" t="s">
         <v>56</v>
       </c>
-      <c r="D10" t="s">
+      <c r="E10" t="s">
+        <v>56</v>
+      </c>
+      <c r="F10" t="s">
+        <v>38</v>
+      </c>
+      <c r="J10" t="s">
         <v>57</v>
       </c>
-      <c r="E10" t="s">
-        <v>57</v>
-      </c>
-      <c r="F10" t="s">
-        <v>39</v>
-      </c>
-      <c r="J10" t="s">
+      <c r="N10" t="s">
         <v>58</v>
-      </c>
-      <c r="N10" t="s">
-        <v>59</v>
       </c>
     </row>
     <row r="11" spans="1:30" x14ac:dyDescent="0.45">
@@ -1761,25 +2586,25 @@
         <v>30</v>
       </c>
       <c r="B11" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C11" t="s">
+        <v>69</v>
+      </c>
+      <c r="D11" t="s">
         <v>70</v>
       </c>
-      <c r="D11" t="s">
+      <c r="E11" t="s">
         <v>71</v>
       </c>
-      <c r="E11" t="s">
-        <v>72</v>
-      </c>
       <c r="F11" t="s">
+        <v>59</v>
+      </c>
+      <c r="J11" t="s">
         <v>60</v>
       </c>
-      <c r="J11" t="s">
+      <c r="N11" t="s">
         <v>61</v>
-      </c>
-      <c r="N11" t="s">
-        <v>62</v>
       </c>
     </row>
     <row r="12" spans="1:30" x14ac:dyDescent="0.45">
@@ -1787,25 +2612,25 @@
         <v>30</v>
       </c>
       <c r="B12" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C12" t="s">
+        <v>72</v>
+      </c>
+      <c r="D12" t="s">
         <v>73</v>
       </c>
-      <c r="D12" t="s">
+      <c r="E12" t="s">
         <v>74</v>
       </c>
-      <c r="E12" t="s">
-        <v>75</v>
-      </c>
       <c r="F12" t="s">
+        <v>59</v>
+      </c>
+      <c r="J12" t="s">
         <v>60</v>
       </c>
-      <c r="J12" t="s">
+      <c r="N12" t="s">
         <v>61</v>
-      </c>
-      <c r="N12" t="s">
-        <v>62</v>
       </c>
     </row>
     <row r="13" spans="1:30" x14ac:dyDescent="0.45">
@@ -1813,25 +2638,25 @@
         <v>30</v>
       </c>
       <c r="B13" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C13" t="s">
+        <v>75</v>
+      </c>
+      <c r="D13" t="s">
         <v>76</v>
       </c>
-      <c r="D13" t="s">
+      <c r="E13" t="s">
         <v>77</v>
       </c>
-      <c r="E13" t="s">
-        <v>78</v>
-      </c>
       <c r="F13" t="s">
+        <v>59</v>
+      </c>
+      <c r="J13" t="s">
         <v>60</v>
       </c>
-      <c r="J13" t="s">
+      <c r="N13" t="s">
         <v>61</v>
-      </c>
-      <c r="N13" t="s">
-        <v>62</v>
       </c>
     </row>
     <row r="14" spans="1:30" x14ac:dyDescent="0.45">
@@ -1839,25 +2664,25 @@
         <v>30</v>
       </c>
       <c r="B14" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C14" t="s">
+        <v>78</v>
+      </c>
+      <c r="D14" t="s">
         <v>79</v>
       </c>
-      <c r="D14" t="s">
+      <c r="E14" t="s">
         <v>80</v>
       </c>
-      <c r="E14" t="s">
-        <v>81</v>
-      </c>
       <c r="F14" t="s">
+        <v>59</v>
+      </c>
+      <c r="J14" t="s">
         <v>60</v>
       </c>
-      <c r="J14" t="s">
+      <c r="N14" t="s">
         <v>61</v>
-      </c>
-      <c r="N14" t="s">
-        <v>62</v>
       </c>
     </row>
     <row r="15" spans="1:30" x14ac:dyDescent="0.45">
@@ -1865,25 +2690,25 @@
         <v>30</v>
       </c>
       <c r="B15" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C15" t="s">
+        <v>81</v>
+      </c>
+      <c r="D15" t="s">
         <v>82</v>
       </c>
-      <c r="D15" t="s">
+      <c r="E15" t="s">
         <v>83</v>
       </c>
-      <c r="E15" t="s">
-        <v>84</v>
-      </c>
       <c r="F15" t="s">
+        <v>59</v>
+      </c>
+      <c r="J15" t="s">
         <v>60</v>
       </c>
-      <c r="J15" t="s">
+      <c r="N15" t="s">
         <v>61</v>
-      </c>
-      <c r="N15" t="s">
-        <v>62</v>
       </c>
     </row>
     <row r="16" spans="1:30" x14ac:dyDescent="0.45">
@@ -1891,25 +2716,25 @@
         <v>30</v>
       </c>
       <c r="B16" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C16" t="s">
+        <v>84</v>
+      </c>
+      <c r="D16" t="s">
         <v>85</v>
       </c>
-      <c r="D16" t="s">
+      <c r="E16" t="s">
         <v>86</v>
       </c>
-      <c r="E16" t="s">
-        <v>87</v>
-      </c>
       <c r="F16" t="s">
+        <v>59</v>
+      </c>
+      <c r="J16" t="s">
         <v>60</v>
       </c>
-      <c r="J16" t="s">
+      <c r="N16" t="s">
         <v>61</v>
-      </c>
-      <c r="N16" t="s">
-        <v>62</v>
       </c>
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.45">
@@ -1917,16 +2742,16 @@
         <v>30</v>
       </c>
       <c r="B17" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C17" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D17" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E17" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="F17" t="s">
         <v>34</v>
@@ -1937,25 +2762,25 @@
         <v>30</v>
       </c>
       <c r="B18" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C18" t="s">
+        <v>88</v>
+      </c>
+      <c r="D18" t="s">
         <v>89</v>
       </c>
-      <c r="D18" t="s">
+      <c r="E18" t="s">
         <v>90</v>
       </c>
-      <c r="E18" t="s">
-        <v>91</v>
-      </c>
       <c r="F18" t="s">
+        <v>59</v>
+      </c>
+      <c r="J18" t="s">
         <v>60</v>
       </c>
-      <c r="J18" t="s">
+      <c r="N18" t="s">
         <v>61</v>
-      </c>
-      <c r="N18" t="s">
-        <v>62</v>
       </c>
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.45">
@@ -1963,25 +2788,25 @@
         <v>30</v>
       </c>
       <c r="B19" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C19" t="s">
+        <v>91</v>
+      </c>
+      <c r="D19" t="s">
         <v>92</v>
       </c>
-      <c r="D19" t="s">
+      <c r="E19" t="s">
         <v>93</v>
       </c>
-      <c r="E19" t="s">
-        <v>94</v>
-      </c>
       <c r="F19" t="s">
+        <v>59</v>
+      </c>
+      <c r="J19" t="s">
         <v>60</v>
       </c>
-      <c r="J19" t="s">
+      <c r="N19" t="s">
         <v>61</v>
-      </c>
-      <c r="N19" t="s">
-        <v>62</v>
       </c>
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.45">
@@ -1989,25 +2814,25 @@
         <v>30</v>
       </c>
       <c r="B20" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C20" t="s">
+        <v>94</v>
+      </c>
+      <c r="D20" t="s">
         <v>95</v>
       </c>
-      <c r="D20" t="s">
+      <c r="E20" t="s">
         <v>96</v>
       </c>
-      <c r="E20" t="s">
-        <v>97</v>
-      </c>
       <c r="F20" t="s">
+        <v>59</v>
+      </c>
+      <c r="J20" t="s">
         <v>60</v>
       </c>
-      <c r="J20" t="s">
+      <c r="N20" t="s">
         <v>61</v>
-      </c>
-      <c r="N20" t="s">
-        <v>62</v>
       </c>
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.45">
@@ -2015,25 +2840,25 @@
         <v>30</v>
       </c>
       <c r="B21" t="s">
+        <v>64</v>
+      </c>
+      <c r="C21" t="s">
+        <v>97</v>
+      </c>
+      <c r="D21" t="s">
+        <v>98</v>
+      </c>
+      <c r="E21" t="s">
+        <v>99</v>
+      </c>
+      <c r="F21" t="s">
+        <v>38</v>
+      </c>
+      <c r="J21" t="s">
+        <v>63</v>
+      </c>
+      <c r="N21" t="s">
         <v>65</v>
-      </c>
-      <c r="C21" t="s">
-        <v>98</v>
-      </c>
-      <c r="D21" t="s">
-        <v>99</v>
-      </c>
-      <c r="E21" t="s">
-        <v>100</v>
-      </c>
-      <c r="F21" t="s">
-        <v>39</v>
-      </c>
-      <c r="J21" t="s">
-        <v>64</v>
-      </c>
-      <c r="N21" t="s">
-        <v>66</v>
       </c>
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.45">
@@ -2041,25 +2866,25 @@
         <v>30</v>
       </c>
       <c r="B22" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C22" t="s">
+        <v>100</v>
+      </c>
+      <c r="D22" t="s">
         <v>101</v>
       </c>
-      <c r="D22" t="s">
+      <c r="E22" t="s">
         <v>102</v>
       </c>
-      <c r="E22" t="s">
+      <c r="F22" t="s">
+        <v>38</v>
+      </c>
+      <c r="J22" t="s">
+        <v>67</v>
+      </c>
+      <c r="N22" t="s">
         <v>103</v>
-      </c>
-      <c r="F22" t="s">
-        <v>39</v>
-      </c>
-      <c r="J22" t="s">
-        <v>68</v>
-      </c>
-      <c r="N22" t="s">
-        <v>104</v>
       </c>
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.45">
@@ -2067,25 +2892,25 @@
         <v>30</v>
       </c>
       <c r="B23" t="s">
+        <v>105</v>
+      </c>
+      <c r="C23" t="s">
         <v>106</v>
       </c>
-      <c r="C23" t="s">
+      <c r="D23" t="s">
         <v>107</v>
       </c>
-      <c r="D23" t="s">
+      <c r="E23" t="s">
         <v>108</v>
       </c>
-      <c r="E23" t="s">
-        <v>109</v>
-      </c>
       <c r="F23" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="J23" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="N23" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.45">
@@ -2093,25 +2918,25 @@
         <v>30</v>
       </c>
       <c r="B24" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C24" t="s">
+        <v>109</v>
+      </c>
+      <c r="D24" t="s">
         <v>110</v>
       </c>
-      <c r="D24" t="s">
+      <c r="E24" t="s">
         <v>111</v>
       </c>
-      <c r="E24" t="s">
-        <v>112</v>
-      </c>
       <c r="F24" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="J24" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="N24" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.45">
@@ -2119,25 +2944,25 @@
         <v>30</v>
       </c>
       <c r="B25" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C25" t="s">
+        <v>112</v>
+      </c>
+      <c r="D25" t="s">
         <v>113</v>
       </c>
-      <c r="D25" t="s">
+      <c r="E25" t="s">
         <v>114</v>
       </c>
-      <c r="E25" t="s">
-        <v>115</v>
-      </c>
       <c r="F25" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="J25" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="N25" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.45">
@@ -2145,25 +2970,25 @@
         <v>30</v>
       </c>
       <c r="B26" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C26" t="s">
+        <v>115</v>
+      </c>
+      <c r="D26" t="s">
         <v>116</v>
       </c>
-      <c r="D26" t="s">
+      <c r="E26" t="s">
         <v>117</v>
       </c>
-      <c r="E26" t="s">
-        <v>118</v>
-      </c>
       <c r="F26" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="J26" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="N26" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.45">
@@ -2171,25 +2996,25 @@
         <v>30</v>
       </c>
       <c r="B27" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C27" t="s">
+        <v>118</v>
+      </c>
+      <c r="D27" t="s">
         <v>119</v>
       </c>
-      <c r="D27" t="s">
+      <c r="E27" t="s">
         <v>120</v>
       </c>
-      <c r="E27" t="s">
-        <v>121</v>
-      </c>
       <c r="F27" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="J27" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="N27" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.45">
@@ -2197,25 +3022,25 @@
         <v>30</v>
       </c>
       <c r="B28" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C28" t="s">
+        <v>121</v>
+      </c>
+      <c r="D28" t="s">
         <v>122</v>
       </c>
-      <c r="D28" t="s">
+      <c r="E28" t="s">
         <v>123</v>
       </c>
-      <c r="E28" t="s">
-        <v>124</v>
-      </c>
       <c r="F28" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="J28" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="N28" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.45">
@@ -2223,16 +3048,16 @@
         <v>30</v>
       </c>
       <c r="B29" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C29" t="s">
+        <v>124</v>
+      </c>
+      <c r="D29" t="s">
+        <v>104</v>
+      </c>
+      <c r="E29" t="s">
         <v>125</v>
-      </c>
-      <c r="D29" t="s">
-        <v>105</v>
-      </c>
-      <c r="E29" t="s">
-        <v>126</v>
       </c>
       <c r="F29" t="s">
         <v>34</v>
@@ -2243,22 +3068,22 @@
         <v>30</v>
       </c>
       <c r="B30" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C30" t="s">
+        <v>126</v>
+      </c>
+      <c r="D30" t="s">
         <v>127</v>
       </c>
-      <c r="D30" t="s">
+      <c r="E30" t="s">
         <v>128</v>
       </c>
-      <c r="E30" t="s">
-        <v>129</v>
-      </c>
       <c r="F30" t="s">
+        <v>47</v>
+      </c>
+      <c r="G30" t="s">
         <v>48</v>
-      </c>
-      <c r="G30" t="s">
-        <v>49</v>
       </c>
     </row>
     <row r="31" spans="1:14" x14ac:dyDescent="0.45">
@@ -2266,16 +3091,16 @@
         <v>30</v>
       </c>
       <c r="B31" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C31" t="s">
+        <v>129</v>
+      </c>
+      <c r="D31" t="s">
         <v>130</v>
       </c>
-      <c r="D31" t="s">
+      <c r="E31" t="s">
         <v>131</v>
-      </c>
-      <c r="E31" t="s">
-        <v>132</v>
       </c>
       <c r="F31" t="s">
         <v>34</v>
@@ -2286,19 +3111,19 @@
         <v>30</v>
       </c>
       <c r="B32" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C32" t="s">
+        <v>132</v>
+      </c>
+      <c r="D32" t="s">
         <v>133</v>
       </c>
-      <c r="D32" t="s">
+      <c r="E32" t="s">
         <v>134</v>
       </c>
-      <c r="E32" t="s">
-        <v>135</v>
-      </c>
       <c r="F32" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.45">
@@ -2306,25 +3131,25 @@
         <v>30</v>
       </c>
       <c r="B33" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C33" t="s">
+        <v>135</v>
+      </c>
+      <c r="D33" t="s">
         <v>136</v>
       </c>
-      <c r="D33" t="s">
+      <c r="E33" t="s">
         <v>137</v>
       </c>
-      <c r="E33" t="s">
-        <v>138</v>
-      </c>
       <c r="F33" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="J33" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="N33" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.45">
@@ -2332,22 +3157,22 @@
         <v>30</v>
       </c>
       <c r="B34" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C34" t="s">
+        <v>138</v>
+      </c>
+      <c r="D34" t="s">
         <v>139</v>
       </c>
-      <c r="D34" t="s">
+      <c r="E34" t="s">
         <v>140</v>
       </c>
-      <c r="E34" t="s">
-        <v>141</v>
-      </c>
       <c r="F34" t="s">
+        <v>47</v>
+      </c>
+      <c r="G34" t="s">
         <v>48</v>
-      </c>
-      <c r="G34" t="s">
-        <v>49</v>
       </c>
     </row>
     <row r="35" spans="1:14" x14ac:dyDescent="0.45">
@@ -2355,19 +3180,19 @@
         <v>30</v>
       </c>
       <c r="B35" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C35" t="s">
+        <v>141</v>
+      </c>
+      <c r="D35" t="s">
         <v>142</v>
       </c>
-      <c r="D35" t="s">
+      <c r="E35" t="s">
         <v>143</v>
       </c>
-      <c r="E35" t="s">
-        <v>144</v>
-      </c>
       <c r="F35" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="36" spans="1:14" x14ac:dyDescent="0.45">
@@ -2375,16 +3200,16 @@
         <v>30</v>
       </c>
       <c r="B36" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C36" t="s">
+        <v>144</v>
+      </c>
+      <c r="D36" t="s">
         <v>145</v>
       </c>
-      <c r="D36" t="s">
+      <c r="E36" t="s">
         <v>146</v>
-      </c>
-      <c r="E36" t="s">
-        <v>147</v>
       </c>
       <c r="F36" t="s">
         <v>34</v>
@@ -2395,22 +3220,22 @@
         <v>30</v>
       </c>
       <c r="B37" t="s">
+        <v>147</v>
+      </c>
+      <c r="C37" t="s">
         <v>148</v>
       </c>
-      <c r="C37" t="s">
+      <c r="D37" t="s">
         <v>149</v>
       </c>
-      <c r="D37" t="s">
-        <v>150</v>
-      </c>
       <c r="E37" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="F37" t="s">
+        <v>47</v>
+      </c>
+      <c r="G37" t="s">
         <v>48</v>
-      </c>
-      <c r="G37" t="s">
-        <v>49</v>
       </c>
     </row>
     <row r="38" spans="1:14" x14ac:dyDescent="0.45">
@@ -2418,22 +3243,22 @@
         <v>30</v>
       </c>
       <c r="B38" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C38" t="s">
+        <v>150</v>
+      </c>
+      <c r="D38" t="s">
         <v>151</v>
       </c>
-      <c r="D38" t="s">
+      <c r="E38" t="s">
+        <v>151</v>
+      </c>
+      <c r="F38" t="s">
         <v>152</v>
       </c>
-      <c r="E38" t="s">
-        <v>152</v>
-      </c>
-      <c r="F38" t="s">
-        <v>153</v>
-      </c>
       <c r="G38" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="39" spans="1:14" x14ac:dyDescent="0.45">
@@ -2441,19 +3266,19 @@
         <v>30</v>
       </c>
       <c r="B39" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C39" t="s">
+        <v>153</v>
+      </c>
+      <c r="D39" t="s">
         <v>154</v>
       </c>
-      <c r="D39" t="s">
-        <v>155</v>
-      </c>
       <c r="E39" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="F39" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="40" spans="1:14" x14ac:dyDescent="0.45">
@@ -2461,19 +3286,19 @@
         <v>30</v>
       </c>
       <c r="B40" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C40" t="s">
+        <v>155</v>
+      </c>
+      <c r="D40" t="s">
         <v>156</v>
       </c>
-      <c r="D40" t="s">
-        <v>157</v>
-      </c>
       <c r="E40" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="F40" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="41" spans="1:14" x14ac:dyDescent="0.45">
@@ -2481,19 +3306,19 @@
         <v>30</v>
       </c>
       <c r="B41" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C41" t="s">
+        <v>157</v>
+      </c>
+      <c r="D41" t="s">
         <v>158</v>
       </c>
-      <c r="D41" t="s">
-        <v>159</v>
-      </c>
       <c r="E41" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="F41" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="42" spans="1:14" x14ac:dyDescent="0.45">
@@ -2501,19 +3326,19 @@
         <v>30</v>
       </c>
       <c r="B42" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C42" t="s">
+        <v>159</v>
+      </c>
+      <c r="D42" t="s">
         <v>160</v>
       </c>
-      <c r="D42" t="s">
-        <v>161</v>
-      </c>
       <c r="E42" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="F42" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="43" spans="1:14" x14ac:dyDescent="0.45">
@@ -2521,19 +3346,19 @@
         <v>30</v>
       </c>
       <c r="B43" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C43" t="s">
+        <v>161</v>
+      </c>
+      <c r="D43" t="s">
         <v>162</v>
       </c>
-      <c r="D43" t="s">
-        <v>163</v>
-      </c>
       <c r="E43" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="F43" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="44" spans="1:14" x14ac:dyDescent="0.45">
@@ -2541,19 +3366,19 @@
         <v>30</v>
       </c>
       <c r="B44" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C44" t="s">
+        <v>163</v>
+      </c>
+      <c r="D44" t="s">
         <v>164</v>
       </c>
-      <c r="D44" t="s">
-        <v>165</v>
-      </c>
       <c r="E44" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="F44" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="45" spans="1:14" x14ac:dyDescent="0.45">
@@ -2561,16 +3386,16 @@
         <v>30</v>
       </c>
       <c r="B45" t="s">
+        <v>165</v>
+      </c>
+      <c r="C45" t="s">
         <v>166</v>
       </c>
-      <c r="C45" t="s">
+      <c r="D45" t="s">
         <v>167</v>
       </c>
-      <c r="D45" t="s">
+      <c r="E45" t="s">
         <v>168</v>
-      </c>
-      <c r="E45" t="s">
-        <v>169</v>
       </c>
       <c r="F45" t="s">
         <v>34</v>
@@ -2581,25 +3406,25 @@
         <v>30</v>
       </c>
       <c r="B46" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C46" t="s">
+        <v>169</v>
+      </c>
+      <c r="D46" t="s">
         <v>170</v>
       </c>
-      <c r="D46" t="s">
+      <c r="E46" t="s">
         <v>171</v>
       </c>
-      <c r="E46" t="s">
-        <v>172</v>
-      </c>
       <c r="F46" t="s">
+        <v>59</v>
+      </c>
+      <c r="J46" t="s">
         <v>60</v>
       </c>
-      <c r="J46" t="s">
+      <c r="N46" t="s">
         <v>61</v>
-      </c>
-      <c r="N46" t="s">
-        <v>62</v>
       </c>
     </row>
     <row r="47" spans="1:14" x14ac:dyDescent="0.45">
@@ -2607,25 +3432,25 @@
         <v>30</v>
       </c>
       <c r="B47" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C47" t="s">
+        <v>172</v>
+      </c>
+      <c r="D47" t="s">
         <v>173</v>
       </c>
-      <c r="D47" t="s">
+      <c r="E47" t="s">
         <v>174</v>
       </c>
-      <c r="E47" t="s">
-        <v>175</v>
-      </c>
       <c r="F47" t="s">
+        <v>59</v>
+      </c>
+      <c r="J47" t="s">
         <v>60</v>
       </c>
-      <c r="J47" t="s">
+      <c r="N47" t="s">
         <v>61</v>
-      </c>
-      <c r="N47" t="s">
-        <v>62</v>
       </c>
     </row>
     <row r="48" spans="1:14" x14ac:dyDescent="0.45">
@@ -2633,25 +3458,25 @@
         <v>30</v>
       </c>
       <c r="B48" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C48" t="s">
+        <v>175</v>
+      </c>
+      <c r="D48" t="s">
         <v>176</v>
       </c>
-      <c r="D48" t="s">
+      <c r="E48" t="s">
         <v>177</v>
       </c>
-      <c r="E48" t="s">
-        <v>178</v>
-      </c>
       <c r="F48" t="s">
+        <v>59</v>
+      </c>
+      <c r="J48" t="s">
         <v>60</v>
       </c>
-      <c r="J48" t="s">
+      <c r="N48" t="s">
         <v>61</v>
-      </c>
-      <c r="N48" t="s">
-        <v>62</v>
       </c>
     </row>
     <row r="49" spans="1:14" x14ac:dyDescent="0.45">
@@ -2659,25 +3484,25 @@
         <v>30</v>
       </c>
       <c r="B49" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C49" t="s">
+        <v>178</v>
+      </c>
+      <c r="D49" t="s">
         <v>179</v>
       </c>
-      <c r="D49" t="s">
+      <c r="E49" t="s">
         <v>180</v>
       </c>
-      <c r="E49" t="s">
-        <v>181</v>
-      </c>
       <c r="F49" t="s">
+        <v>59</v>
+      </c>
+      <c r="J49" t="s">
         <v>60</v>
       </c>
-      <c r="J49" t="s">
+      <c r="N49" t="s">
         <v>61</v>
-      </c>
-      <c r="N49" t="s">
-        <v>62</v>
       </c>
     </row>
     <row r="50" spans="1:14" x14ac:dyDescent="0.45">
@@ -2685,25 +3510,25 @@
         <v>30</v>
       </c>
       <c r="B50" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C50" t="s">
+        <v>181</v>
+      </c>
+      <c r="D50" t="s">
         <v>182</v>
       </c>
-      <c r="D50" t="s">
+      <c r="E50" t="s">
         <v>183</v>
       </c>
-      <c r="E50" t="s">
-        <v>184</v>
-      </c>
       <c r="F50" t="s">
+        <v>59</v>
+      </c>
+      <c r="J50" t="s">
         <v>60</v>
       </c>
-      <c r="J50" t="s">
+      <c r="N50" t="s">
         <v>61</v>
-      </c>
-      <c r="N50" t="s">
-        <v>62</v>
       </c>
     </row>
     <row r="51" spans="1:14" x14ac:dyDescent="0.45">
@@ -2711,25 +3536,25 @@
         <v>30</v>
       </c>
       <c r="B51" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C51" t="s">
+        <v>184</v>
+      </c>
+      <c r="D51" t="s">
         <v>185</v>
       </c>
-      <c r="D51" t="s">
+      <c r="E51" t="s">
         <v>186</v>
       </c>
-      <c r="E51" t="s">
-        <v>187</v>
-      </c>
       <c r="F51" t="s">
+        <v>59</v>
+      </c>
+      <c r="J51" t="s">
         <v>60</v>
       </c>
-      <c r="J51" t="s">
+      <c r="N51" t="s">
         <v>61</v>
-      </c>
-      <c r="N51" t="s">
-        <v>62</v>
       </c>
     </row>
     <row r="52" spans="1:14" x14ac:dyDescent="0.45">
@@ -2737,25 +3562,2939 @@
         <v>30</v>
       </c>
       <c r="B52" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C52" t="s">
+        <v>187</v>
+      </c>
+      <c r="D52" t="s">
         <v>188</v>
       </c>
-      <c r="D52" t="s">
+      <c r="E52" t="s">
         <v>189</v>
       </c>
-      <c r="E52" t="s">
+      <c r="F52" t="s">
+        <v>59</v>
+      </c>
+      <c r="J52" t="s">
+        <v>60</v>
+      </c>
+      <c r="N52" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="53" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A53" t="s">
+        <v>30</v>
+      </c>
+      <c r="B53" t="s">
         <v>190</v>
       </c>
-      <c r="F52" t="s">
+      <c r="C53" t="s">
+        <v>191</v>
+      </c>
+      <c r="D53" t="s">
+        <v>192</v>
+      </c>
+      <c r="E53" t="s">
+        <v>192</v>
+      </c>
+      <c r="F53" t="s">
+        <v>38</v>
+      </c>
+      <c r="J53" t="s">
+        <v>193</v>
+      </c>
+      <c r="N53" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="54" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A54" t="s">
+        <v>30</v>
+      </c>
+      <c r="B54" t="s">
+        <v>190</v>
+      </c>
+      <c r="C54" t="s">
+        <v>195</v>
+      </c>
+      <c r="D54" t="s">
+        <v>196</v>
+      </c>
+      <c r="E54" t="s">
+        <v>196</v>
+      </c>
+      <c r="F54" t="s">
+        <v>38</v>
+      </c>
+      <c r="J54" t="s">
+        <v>193</v>
+      </c>
+      <c r="N54" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="55" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A55" t="s">
+        <v>30</v>
+      </c>
+      <c r="B55" t="s">
+        <v>190</v>
+      </c>
+      <c r="C55" t="s">
+        <v>197</v>
+      </c>
+      <c r="D55" t="s">
+        <v>198</v>
+      </c>
+      <c r="E55" t="s">
+        <v>198</v>
+      </c>
+      <c r="F55" t="s">
+        <v>38</v>
+      </c>
+      <c r="J55" t="s">
+        <v>193</v>
+      </c>
+      <c r="N55" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="56" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A56" t="s">
+        <v>30</v>
+      </c>
+      <c r="B56" t="s">
+        <v>190</v>
+      </c>
+      <c r="C56" t="s">
+        <v>199</v>
+      </c>
+      <c r="D56" t="s">
+        <v>200</v>
+      </c>
+      <c r="E56" t="s">
+        <v>200</v>
+      </c>
+      <c r="F56" t="s">
+        <v>38</v>
+      </c>
+      <c r="J56" t="s">
+        <v>193</v>
+      </c>
+      <c r="N56" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="57" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A57" t="s">
+        <v>30</v>
+      </c>
+      <c r="B57" t="s">
+        <v>190</v>
+      </c>
+      <c r="C57" t="s">
+        <v>201</v>
+      </c>
+      <c r="D57" t="s">
+        <v>202</v>
+      </c>
+      <c r="E57" t="s">
+        <v>202</v>
+      </c>
+      <c r="F57" t="s">
+        <v>38</v>
+      </c>
+      <c r="J57" t="s">
+        <v>193</v>
+      </c>
+      <c r="N57" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="58" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A58" t="s">
+        <v>30</v>
+      </c>
+      <c r="B58" t="s">
+        <v>190</v>
+      </c>
+      <c r="C58" t="s">
+        <v>203</v>
+      </c>
+      <c r="D58" t="s">
+        <v>204</v>
+      </c>
+      <c r="E58" t="s">
+        <v>204</v>
+      </c>
+      <c r="F58" t="s">
+        <v>38</v>
+      </c>
+      <c r="J58" t="s">
+        <v>193</v>
+      </c>
+      <c r="N58" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="59" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A59" t="s">
+        <v>30</v>
+      </c>
+      <c r="B59" t="s">
+        <v>190</v>
+      </c>
+      <c r="C59" t="s">
+        <v>205</v>
+      </c>
+      <c r="D59" t="s">
+        <v>206</v>
+      </c>
+      <c r="E59" t="s">
+        <v>206</v>
+      </c>
+      <c r="F59" t="s">
+        <v>38</v>
+      </c>
+      <c r="J59" t="s">
+        <v>193</v>
+      </c>
+      <c r="N59" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="60" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A60" t="s">
+        <v>30</v>
+      </c>
+      <c r="B60" t="s">
+        <v>207</v>
+      </c>
+      <c r="C60" t="s">
+        <v>208</v>
+      </c>
+      <c r="D60" t="s">
+        <v>209</v>
+      </c>
+      <c r="E60" t="s">
+        <v>209</v>
+      </c>
+      <c r="F60" t="s">
+        <v>38</v>
+      </c>
+      <c r="J60" t="s">
+        <v>193</v>
+      </c>
+      <c r="N60" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="61" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A61" t="s">
+        <v>30</v>
+      </c>
+      <c r="B61" t="s">
+        <v>207</v>
+      </c>
+      <c r="C61" t="s">
+        <v>211</v>
+      </c>
+      <c r="D61" t="s">
+        <v>212</v>
+      </c>
+      <c r="E61" t="s">
+        <v>212</v>
+      </c>
+      <c r="F61" t="s">
+        <v>38</v>
+      </c>
+      <c r="J61" t="s">
+        <v>193</v>
+      </c>
+      <c r="N61" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="62" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A62" t="s">
+        <v>30</v>
+      </c>
+      <c r="B62" t="s">
+        <v>207</v>
+      </c>
+      <c r="C62" t="s">
+        <v>213</v>
+      </c>
+      <c r="D62" t="s">
+        <v>214</v>
+      </c>
+      <c r="E62" t="s">
+        <v>214</v>
+      </c>
+      <c r="F62" t="s">
+        <v>38</v>
+      </c>
+      <c r="J62" t="s">
+        <v>193</v>
+      </c>
+      <c r="N62" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="63" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A63" t="s">
+        <v>30</v>
+      </c>
+      <c r="B63" t="s">
+        <v>207</v>
+      </c>
+      <c r="C63" t="s">
+        <v>215</v>
+      </c>
+      <c r="D63" t="s">
+        <v>216</v>
+      </c>
+      <c r="E63" t="s">
+        <v>216</v>
+      </c>
+      <c r="F63" t="s">
+        <v>38</v>
+      </c>
+      <c r="J63" t="s">
+        <v>193</v>
+      </c>
+      <c r="N63" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="64" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A64" t="s">
+        <v>30</v>
+      </c>
+      <c r="B64" t="s">
+        <v>217</v>
+      </c>
+      <c r="C64" t="s">
+        <v>218</v>
+      </c>
+      <c r="D64" t="s">
+        <v>219</v>
+      </c>
+      <c r="E64" t="s">
+        <v>219</v>
+      </c>
+      <c r="F64" t="s">
+        <v>38</v>
+      </c>
+      <c r="J64" t="s">
+        <v>220</v>
+      </c>
+      <c r="N64" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="65" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A65" t="s">
+        <v>30</v>
+      </c>
+      <c r="B65" t="s">
+        <v>217</v>
+      </c>
+      <c r="C65" t="s">
+        <v>222</v>
+      </c>
+      <c r="D65" t="s">
+        <v>223</v>
+      </c>
+      <c r="E65" t="s">
+        <v>223</v>
+      </c>
+      <c r="F65" t="s">
+        <v>38</v>
+      </c>
+      <c r="J65" t="s">
+        <v>220</v>
+      </c>
+      <c r="N65" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="66" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A66" t="s">
+        <v>30</v>
+      </c>
+      <c r="B66" t="s">
+        <v>217</v>
+      </c>
+      <c r="C66" t="s">
+        <v>224</v>
+      </c>
+      <c r="D66" t="s">
+        <v>225</v>
+      </c>
+      <c r="E66" t="s">
+        <v>225</v>
+      </c>
+      <c r="F66" t="s">
+        <v>38</v>
+      </c>
+      <c r="J66" t="s">
+        <v>220</v>
+      </c>
+      <c r="N66" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="67" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A67" t="s">
+        <v>30</v>
+      </c>
+      <c r="B67" t="s">
+        <v>217</v>
+      </c>
+      <c r="C67" t="s">
+        <v>226</v>
+      </c>
+      <c r="D67" t="s">
+        <v>227</v>
+      </c>
+      <c r="E67" t="s">
+        <v>227</v>
+      </c>
+      <c r="F67" t="s">
+        <v>38</v>
+      </c>
+      <c r="J67" t="s">
+        <v>220</v>
+      </c>
+      <c r="N67" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="68" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A68" t="s">
+        <v>30</v>
+      </c>
+      <c r="B68" t="s">
+        <v>217</v>
+      </c>
+      <c r="C68" t="s">
+        <v>228</v>
+      </c>
+      <c r="D68" t="s">
+        <v>229</v>
+      </c>
+      <c r="E68" t="s">
+        <v>229</v>
+      </c>
+      <c r="F68" t="s">
+        <v>38</v>
+      </c>
+      <c r="J68" t="s">
+        <v>220</v>
+      </c>
+      <c r="N68" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="69" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A69" t="s">
+        <v>30</v>
+      </c>
+      <c r="B69" t="s">
+        <v>217</v>
+      </c>
+      <c r="C69" t="s">
+        <v>230</v>
+      </c>
+      <c r="D69" t="s">
+        <v>231</v>
+      </c>
+      <c r="E69" t="s">
+        <v>231</v>
+      </c>
+      <c r="F69" t="s">
+        <v>38</v>
+      </c>
+      <c r="J69" t="s">
+        <v>220</v>
+      </c>
+      <c r="N69" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="70" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A70" t="s">
+        <v>30</v>
+      </c>
+      <c r="B70" t="s">
+        <v>217</v>
+      </c>
+      <c r="C70" t="s">
+        <v>232</v>
+      </c>
+      <c r="D70" t="s">
+        <v>233</v>
+      </c>
+      <c r="E70" t="s">
+        <v>233</v>
+      </c>
+      <c r="F70" t="s">
+        <v>38</v>
+      </c>
+      <c r="J70" t="s">
+        <v>220</v>
+      </c>
+      <c r="N70" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="71" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A71" t="s">
+        <v>30</v>
+      </c>
+      <c r="B71" t="s">
+        <v>234</v>
+      </c>
+      <c r="C71" t="s">
+        <v>235</v>
+      </c>
+      <c r="D71" t="s">
+        <v>236</v>
+      </c>
+      <c r="E71" t="s">
+        <v>236</v>
+      </c>
+      <c r="F71" t="s">
+        <v>38</v>
+      </c>
+      <c r="J71" t="s">
+        <v>237</v>
+      </c>
+      <c r="N71" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="72" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A72" t="s">
+        <v>30</v>
+      </c>
+      <c r="B72" t="s">
+        <v>234</v>
+      </c>
+      <c r="C72" t="s">
+        <v>239</v>
+      </c>
+      <c r="D72" t="s">
+        <v>240</v>
+      </c>
+      <c r="E72" t="s">
+        <v>240</v>
+      </c>
+      <c r="F72" t="s">
+        <v>38</v>
+      </c>
+      <c r="J72" t="s">
+        <v>237</v>
+      </c>
+      <c r="N72" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="73" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A73" t="s">
+        <v>30</v>
+      </c>
+      <c r="B73" t="s">
+        <v>234</v>
+      </c>
+      <c r="C73" t="s">
+        <v>241</v>
+      </c>
+      <c r="D73" t="s">
+        <v>242</v>
+      </c>
+      <c r="E73" t="s">
+        <v>242</v>
+      </c>
+      <c r="F73" t="s">
+        <v>38</v>
+      </c>
+      <c r="J73" t="s">
+        <v>237</v>
+      </c>
+      <c r="N73" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="74" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A74" t="s">
+        <v>30</v>
+      </c>
+      <c r="B74" t="s">
+        <v>234</v>
+      </c>
+      <c r="C74" t="s">
+        <v>243</v>
+      </c>
+      <c r="D74" t="s">
+        <v>244</v>
+      </c>
+      <c r="E74" t="s">
+        <v>244</v>
+      </c>
+      <c r="F74" t="s">
+        <v>38</v>
+      </c>
+      <c r="J74" t="s">
+        <v>237</v>
+      </c>
+      <c r="N74" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="75" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A75" t="s">
+        <v>30</v>
+      </c>
+      <c r="B75" t="s">
+        <v>234</v>
+      </c>
+      <c r="C75" t="s">
+        <v>245</v>
+      </c>
+      <c r="D75" t="s">
+        <v>246</v>
+      </c>
+      <c r="E75" t="s">
+        <v>246</v>
+      </c>
+      <c r="F75" t="s">
+        <v>38</v>
+      </c>
+      <c r="J75" t="s">
+        <v>237</v>
+      </c>
+      <c r="N75" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="76" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A76" t="s">
+        <v>30</v>
+      </c>
+      <c r="B76" t="s">
+        <v>234</v>
+      </c>
+      <c r="C76" t="s">
+        <v>247</v>
+      </c>
+      <c r="D76" t="s">
+        <v>248</v>
+      </c>
+      <c r="E76" t="s">
+        <v>248</v>
+      </c>
+      <c r="F76" t="s">
+        <v>38</v>
+      </c>
+      <c r="J76" t="s">
+        <v>237</v>
+      </c>
+      <c r="N76" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="77" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A77" t="s">
+        <v>30</v>
+      </c>
+      <c r="B77" t="s">
+        <v>249</v>
+      </c>
+      <c r="C77" t="s">
+        <v>250</v>
+      </c>
+      <c r="D77" t="s">
+        <v>251</v>
+      </c>
+      <c r="E77" t="s">
+        <v>251</v>
+      </c>
+      <c r="F77" t="s">
+        <v>38</v>
+      </c>
+      <c r="J77" t="s">
         <v>60</v>
       </c>
-      <c r="J52" t="s">
-        <v>61</v>
-      </c>
-      <c r="N52" t="s">
-        <v>62</v>
+      <c r="N77" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="78" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A78" t="s">
+        <v>30</v>
+      </c>
+      <c r="B78" t="s">
+        <v>249</v>
+      </c>
+      <c r="C78" t="s">
+        <v>253</v>
+      </c>
+      <c r="D78" t="s">
+        <v>254</v>
+      </c>
+      <c r="E78" t="s">
+        <v>254</v>
+      </c>
+      <c r="F78" t="s">
+        <v>38</v>
+      </c>
+      <c r="J78" t="s">
+        <v>255</v>
+      </c>
+      <c r="N78" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="79" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A79" t="s">
+        <v>30</v>
+      </c>
+      <c r="B79" t="s">
+        <v>249</v>
+      </c>
+      <c r="C79" t="s">
+        <v>257</v>
+      </c>
+      <c r="D79" t="s">
+        <v>258</v>
+      </c>
+      <c r="E79" t="s">
+        <v>258</v>
+      </c>
+      <c r="F79" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="80" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A80" t="s">
+        <v>30</v>
+      </c>
+      <c r="B80" t="s">
+        <v>249</v>
+      </c>
+      <c r="C80" t="s">
+        <v>259</v>
+      </c>
+      <c r="D80" t="s">
+        <v>260</v>
+      </c>
+      <c r="E80" t="s">
+        <v>260</v>
+      </c>
+      <c r="F80" t="s">
+        <v>38</v>
+      </c>
+      <c r="J80" t="s">
+        <v>261</v>
+      </c>
+      <c r="N80" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="81" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A81" t="s">
+        <v>30</v>
+      </c>
+      <c r="B81" t="s">
+        <v>249</v>
+      </c>
+      <c r="C81" t="s">
+        <v>263</v>
+      </c>
+      <c r="D81" t="s">
+        <v>264</v>
+      </c>
+      <c r="E81" t="s">
+        <v>264</v>
+      </c>
+      <c r="F81" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="82" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A82" t="s">
+        <v>30</v>
+      </c>
+      <c r="B82" t="s">
+        <v>249</v>
+      </c>
+      <c r="C82" t="s">
+        <v>265</v>
+      </c>
+      <c r="D82" t="s">
+        <v>266</v>
+      </c>
+      <c r="E82" t="s">
+        <v>266</v>
+      </c>
+      <c r="F82" t="s">
+        <v>38</v>
+      </c>
+      <c r="J82" t="s">
+        <v>60</v>
+      </c>
+      <c r="N82" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="83" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A83" t="s">
+        <v>30</v>
+      </c>
+      <c r="B83" t="s">
+        <v>267</v>
+      </c>
+      <c r="C83" t="s">
+        <v>268</v>
+      </c>
+      <c r="D83" t="s">
+        <v>269</v>
+      </c>
+      <c r="E83" t="s">
+        <v>269</v>
+      </c>
+      <c r="F83" t="s">
+        <v>38</v>
+      </c>
+      <c r="J83" t="s">
+        <v>60</v>
+      </c>
+      <c r="N83" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="84" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A84" t="s">
+        <v>30</v>
+      </c>
+      <c r="B84" t="s">
+        <v>267</v>
+      </c>
+      <c r="C84" t="s">
+        <v>270</v>
+      </c>
+      <c r="D84" t="s">
+        <v>271</v>
+      </c>
+      <c r="E84" t="s">
+        <v>271</v>
+      </c>
+      <c r="F84" t="s">
+        <v>38</v>
+      </c>
+      <c r="J84" t="s">
+        <v>255</v>
+      </c>
+      <c r="N84" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="85" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A85" t="s">
+        <v>30</v>
+      </c>
+      <c r="B85" t="s">
+        <v>267</v>
+      </c>
+      <c r="C85" t="s">
+        <v>273</v>
+      </c>
+      <c r="D85" t="s">
+        <v>274</v>
+      </c>
+      <c r="E85" t="s">
+        <v>274</v>
+      </c>
+      <c r="F85" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="86" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A86" t="s">
+        <v>30</v>
+      </c>
+      <c r="B86" t="s">
+        <v>267</v>
+      </c>
+      <c r="C86" t="s">
+        <v>275</v>
+      </c>
+      <c r="D86" t="s">
+        <v>276</v>
+      </c>
+      <c r="E86" t="s">
+        <v>276</v>
+      </c>
+      <c r="F86" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="87" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A87" t="s">
+        <v>30</v>
+      </c>
+      <c r="B87" t="s">
+        <v>267</v>
+      </c>
+      <c r="C87" t="s">
+        <v>277</v>
+      </c>
+      <c r="D87" t="s">
+        <v>278</v>
+      </c>
+      <c r="E87" t="s">
+        <v>278</v>
+      </c>
+      <c r="F87" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="88" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A88" t="s">
+        <v>30</v>
+      </c>
+      <c r="B88" t="s">
+        <v>267</v>
+      </c>
+      <c r="C88" t="s">
+        <v>279</v>
+      </c>
+      <c r="D88" t="s">
+        <v>280</v>
+      </c>
+      <c r="E88" t="s">
+        <v>280</v>
+      </c>
+      <c r="F88" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="89" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A89" t="s">
+        <v>30</v>
+      </c>
+      <c r="B89" t="s">
+        <v>267</v>
+      </c>
+      <c r="C89" t="s">
+        <v>281</v>
+      </c>
+      <c r="D89" t="s">
+        <v>282</v>
+      </c>
+      <c r="E89" t="s">
+        <v>282</v>
+      </c>
+      <c r="F89" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="90" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A90" t="s">
+        <v>30</v>
+      </c>
+      <c r="B90" t="s">
+        <v>267</v>
+      </c>
+      <c r="C90" t="s">
+        <v>283</v>
+      </c>
+      <c r="D90" t="s">
+        <v>284</v>
+      </c>
+      <c r="E90" t="s">
+        <v>284</v>
+      </c>
+      <c r="F90" t="s">
+        <v>38</v>
+      </c>
+      <c r="J90" t="s">
+        <v>285</v>
+      </c>
+      <c r="N90" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="91" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A91" t="s">
+        <v>30</v>
+      </c>
+      <c r="B91" t="s">
+        <v>287</v>
+      </c>
+      <c r="C91" t="s">
+        <v>288</v>
+      </c>
+      <c r="D91" t="s">
+        <v>289</v>
+      </c>
+      <c r="E91" t="s">
+        <v>289</v>
+      </c>
+      <c r="F91" t="s">
+        <v>38</v>
+      </c>
+      <c r="J91" t="s">
+        <v>290</v>
+      </c>
+      <c r="N91" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="92" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A92" t="s">
+        <v>30</v>
+      </c>
+      <c r="B92" t="s">
+        <v>287</v>
+      </c>
+      <c r="C92" t="s">
+        <v>292</v>
+      </c>
+      <c r="D92" t="s">
+        <v>293</v>
+      </c>
+      <c r="E92" t="s">
+        <v>293</v>
+      </c>
+      <c r="F92" t="s">
+        <v>38</v>
+      </c>
+      <c r="J92" t="s">
+        <v>60</v>
+      </c>
+      <c r="N92" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="93" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A93" t="s">
+        <v>30</v>
+      </c>
+      <c r="B93" t="s">
+        <v>287</v>
+      </c>
+      <c r="C93" t="s">
+        <v>294</v>
+      </c>
+      <c r="D93" t="s">
+        <v>295</v>
+      </c>
+      <c r="E93" t="s">
+        <v>295</v>
+      </c>
+      <c r="F93" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="94" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A94" t="s">
+        <v>30</v>
+      </c>
+      <c r="B94" t="s">
+        <v>287</v>
+      </c>
+      <c r="C94" t="s">
+        <v>296</v>
+      </c>
+      <c r="D94" t="s">
+        <v>297</v>
+      </c>
+      <c r="E94" t="s">
+        <v>297</v>
+      </c>
+      <c r="F94" t="s">
+        <v>38</v>
+      </c>
+      <c r="J94" t="s">
+        <v>60</v>
+      </c>
+      <c r="N94" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="95" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A95" t="s">
+        <v>30</v>
+      </c>
+      <c r="B95" t="s">
+        <v>287</v>
+      </c>
+      <c r="C95" t="s">
+        <v>298</v>
+      </c>
+      <c r="D95" t="s">
+        <v>299</v>
+      </c>
+      <c r="E95" t="s">
+        <v>299</v>
+      </c>
+      <c r="F95" t="s">
+        <v>38</v>
+      </c>
+      <c r="J95" t="s">
+        <v>261</v>
+      </c>
+      <c r="N95" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="96" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A96" t="s">
+        <v>30</v>
+      </c>
+      <c r="B96" t="s">
+        <v>287</v>
+      </c>
+      <c r="C96" t="s">
+        <v>301</v>
+      </c>
+      <c r="D96" t="s">
+        <v>302</v>
+      </c>
+      <c r="E96" t="s">
+        <v>302</v>
+      </c>
+      <c r="F96" t="s">
+        <v>38</v>
+      </c>
+      <c r="J96" t="s">
+        <v>303</v>
+      </c>
+      <c r="N96" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="97" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A97" t="s">
+        <v>30</v>
+      </c>
+      <c r="B97" t="s">
+        <v>287</v>
+      </c>
+      <c r="C97" t="s">
+        <v>305</v>
+      </c>
+      <c r="D97" t="s">
+        <v>306</v>
+      </c>
+      <c r="E97" t="s">
+        <v>306</v>
+      </c>
+      <c r="F97" t="s">
+        <v>38</v>
+      </c>
+      <c r="J97" t="s">
+        <v>307</v>
+      </c>
+      <c r="N97" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="98" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A98" t="s">
+        <v>30</v>
+      </c>
+      <c r="B98" t="s">
+        <v>287</v>
+      </c>
+      <c r="C98" t="s">
+        <v>309</v>
+      </c>
+      <c r="D98" t="s">
+        <v>310</v>
+      </c>
+      <c r="E98" t="s">
+        <v>310</v>
+      </c>
+      <c r="F98" t="s">
+        <v>38</v>
+      </c>
+      <c r="J98" t="s">
+        <v>307</v>
+      </c>
+      <c r="N98" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="99" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A99" t="s">
+        <v>30</v>
+      </c>
+      <c r="B99" t="s">
+        <v>287</v>
+      </c>
+      <c r="C99" t="s">
+        <v>311</v>
+      </c>
+      <c r="D99" t="s">
+        <v>312</v>
+      </c>
+      <c r="E99" t="s">
+        <v>312</v>
+      </c>
+      <c r="F99" t="s">
+        <v>38</v>
+      </c>
+      <c r="J99" t="s">
+        <v>57</v>
+      </c>
+      <c r="N99" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="100" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A100" t="s">
+        <v>30</v>
+      </c>
+      <c r="B100" t="s">
+        <v>287</v>
+      </c>
+      <c r="C100" t="s">
+        <v>314</v>
+      </c>
+      <c r="D100" t="s">
+        <v>315</v>
+      </c>
+      <c r="E100" t="s">
+        <v>315</v>
+      </c>
+      <c r="F100" t="s">
+        <v>38</v>
+      </c>
+      <c r="J100" t="s">
+        <v>316</v>
+      </c>
+      <c r="N100" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="101" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A101" t="s">
+        <v>30</v>
+      </c>
+      <c r="B101" t="s">
+        <v>287</v>
+      </c>
+      <c r="C101" t="s">
+        <v>318</v>
+      </c>
+      <c r="D101" t="s">
+        <v>319</v>
+      </c>
+      <c r="E101" t="s">
+        <v>319</v>
+      </c>
+      <c r="F101" t="s">
+        <v>38</v>
+      </c>
+      <c r="J101" t="s">
+        <v>307</v>
+      </c>
+      <c r="N101" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="102" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A102" t="s">
+        <v>30</v>
+      </c>
+      <c r="B102" t="s">
+        <v>287</v>
+      </c>
+      <c r="C102" t="s">
+        <v>320</v>
+      </c>
+      <c r="D102" t="s">
+        <v>321</v>
+      </c>
+      <c r="E102" t="s">
+        <v>321</v>
+      </c>
+      <c r="F102" t="s">
+        <v>38</v>
+      </c>
+      <c r="J102" t="s">
+        <v>307</v>
+      </c>
+      <c r="N102" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="103" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A103" t="s">
+        <v>30</v>
+      </c>
+      <c r="B103" t="s">
+        <v>287</v>
+      </c>
+      <c r="C103" t="s">
+        <v>322</v>
+      </c>
+      <c r="D103" t="s">
+        <v>323</v>
+      </c>
+      <c r="E103" t="s">
+        <v>323</v>
+      </c>
+      <c r="F103" t="s">
+        <v>38</v>
+      </c>
+      <c r="J103" t="s">
+        <v>307</v>
+      </c>
+      <c r="N103" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="104" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A104" t="s">
+        <v>30</v>
+      </c>
+      <c r="B104" t="s">
+        <v>287</v>
+      </c>
+      <c r="C104" t="s">
+        <v>324</v>
+      </c>
+      <c r="D104" t="s">
+        <v>325</v>
+      </c>
+      <c r="E104" t="s">
+        <v>325</v>
+      </c>
+      <c r="F104" t="s">
+        <v>38</v>
+      </c>
+      <c r="J104" t="s">
+        <v>307</v>
+      </c>
+      <c r="N104" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="105" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A105" t="s">
+        <v>30</v>
+      </c>
+      <c r="B105" t="s">
+        <v>287</v>
+      </c>
+      <c r="C105" t="s">
+        <v>326</v>
+      </c>
+      <c r="D105" t="s">
+        <v>327</v>
+      </c>
+      <c r="E105" t="s">
+        <v>327</v>
+      </c>
+      <c r="F105" t="s">
+        <v>38</v>
+      </c>
+      <c r="J105" t="s">
+        <v>307</v>
+      </c>
+      <c r="N105" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="106" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A106" t="s">
+        <v>30</v>
+      </c>
+      <c r="B106" t="s">
+        <v>287</v>
+      </c>
+      <c r="C106" t="s">
+        <v>328</v>
+      </c>
+      <c r="D106" t="s">
+        <v>329</v>
+      </c>
+      <c r="E106" t="s">
+        <v>329</v>
+      </c>
+      <c r="F106" t="s">
+        <v>38</v>
+      </c>
+      <c r="J106" t="s">
+        <v>307</v>
+      </c>
+      <c r="N106" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="107" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A107" t="s">
+        <v>30</v>
+      </c>
+      <c r="B107" t="s">
+        <v>287</v>
+      </c>
+      <c r="C107" t="s">
+        <v>330</v>
+      </c>
+      <c r="D107" t="s">
+        <v>331</v>
+      </c>
+      <c r="E107" t="s">
+        <v>331</v>
+      </c>
+      <c r="F107" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="108" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A108" t="s">
+        <v>30</v>
+      </c>
+      <c r="B108" t="s">
+        <v>287</v>
+      </c>
+      <c r="C108" t="s">
+        <v>332</v>
+      </c>
+      <c r="D108" t="s">
+        <v>333</v>
+      </c>
+      <c r="E108" t="s">
+        <v>333</v>
+      </c>
+      <c r="F108" t="s">
+        <v>38</v>
+      </c>
+      <c r="J108" t="s">
+        <v>307</v>
+      </c>
+      <c r="N108" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="109" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A109" t="s">
+        <v>30</v>
+      </c>
+      <c r="B109" t="s">
+        <v>287</v>
+      </c>
+      <c r="C109" t="s">
+        <v>334</v>
+      </c>
+      <c r="D109" t="s">
+        <v>335</v>
+      </c>
+      <c r="E109" t="s">
+        <v>335</v>
+      </c>
+      <c r="F109" t="s">
+        <v>38</v>
+      </c>
+      <c r="J109" t="s">
+        <v>336</v>
+      </c>
+      <c r="N109" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="110" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A110" t="s">
+        <v>30</v>
+      </c>
+      <c r="B110" t="s">
+        <v>287</v>
+      </c>
+      <c r="C110" t="s">
+        <v>338</v>
+      </c>
+      <c r="D110" t="s">
+        <v>339</v>
+      </c>
+      <c r="E110" t="s">
+        <v>339</v>
+      </c>
+      <c r="F110" t="s">
+        <v>38</v>
+      </c>
+      <c r="J110" t="s">
+        <v>316</v>
+      </c>
+      <c r="N110" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="111" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A111" t="s">
+        <v>30</v>
+      </c>
+      <c r="B111" t="s">
+        <v>287</v>
+      </c>
+      <c r="C111" t="s">
+        <v>341</v>
+      </c>
+      <c r="D111" t="s">
+        <v>342</v>
+      </c>
+      <c r="E111" t="s">
+        <v>342</v>
+      </c>
+      <c r="F111" t="s">
+        <v>38</v>
+      </c>
+      <c r="J111" t="s">
+        <v>60</v>
+      </c>
+      <c r="N111" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="112" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A112" t="s">
+        <v>30</v>
+      </c>
+      <c r="B112" t="s">
+        <v>287</v>
+      </c>
+      <c r="C112" t="s">
+        <v>343</v>
+      </c>
+      <c r="D112" t="s">
+        <v>344</v>
+      </c>
+      <c r="E112" t="s">
+        <v>344</v>
+      </c>
+      <c r="F112" t="s">
+        <v>345</v>
+      </c>
+      <c r="G112" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="113" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A113" t="s">
+        <v>30</v>
+      </c>
+      <c r="B113" t="s">
+        <v>287</v>
+      </c>
+      <c r="C113" t="s">
+        <v>346</v>
+      </c>
+      <c r="D113" t="s">
+        <v>347</v>
+      </c>
+      <c r="E113" t="s">
+        <v>347</v>
+      </c>
+      <c r="F113" t="s">
+        <v>345</v>
+      </c>
+      <c r="G113" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="114" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A114" t="s">
+        <v>30</v>
+      </c>
+      <c r="B114" t="s">
+        <v>287</v>
+      </c>
+      <c r="C114" t="s">
+        <v>348</v>
+      </c>
+      <c r="D114" t="s">
+        <v>349</v>
+      </c>
+      <c r="E114" t="s">
+        <v>349</v>
+      </c>
+      <c r="F114" t="s">
+        <v>38</v>
+      </c>
+      <c r="J114" t="s">
+        <v>307</v>
+      </c>
+      <c r="N114" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="115" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A115" t="s">
+        <v>30</v>
+      </c>
+      <c r="B115" t="s">
+        <v>287</v>
+      </c>
+      <c r="C115" t="s">
+        <v>350</v>
+      </c>
+      <c r="D115" t="s">
+        <v>351</v>
+      </c>
+      <c r="E115" t="s">
+        <v>351</v>
+      </c>
+      <c r="F115" t="s">
+        <v>38</v>
+      </c>
+      <c r="J115" t="s">
+        <v>307</v>
+      </c>
+      <c r="N115" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="116" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A116" t="s">
+        <v>30</v>
+      </c>
+      <c r="B116" t="s">
+        <v>287</v>
+      </c>
+      <c r="C116" t="s">
+        <v>352</v>
+      </c>
+      <c r="D116" t="s">
+        <v>353</v>
+      </c>
+      <c r="E116" t="s">
+        <v>353</v>
+      </c>
+      <c r="F116" t="s">
+        <v>38</v>
+      </c>
+      <c r="J116" t="s">
+        <v>60</v>
+      </c>
+      <c r="N116" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="117" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A117" t="s">
+        <v>30</v>
+      </c>
+      <c r="B117" t="s">
+        <v>287</v>
+      </c>
+      <c r="C117" t="s">
+        <v>354</v>
+      </c>
+      <c r="D117" t="s">
+        <v>355</v>
+      </c>
+      <c r="E117" t="s">
+        <v>355</v>
+      </c>
+      <c r="F117" t="s">
+        <v>38</v>
+      </c>
+      <c r="J117" t="s">
+        <v>60</v>
+      </c>
+      <c r="N117" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="118" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A118" t="s">
+        <v>30</v>
+      </c>
+      <c r="B118" t="s">
+        <v>287</v>
+      </c>
+      <c r="C118" t="s">
+        <v>356</v>
+      </c>
+      <c r="D118" t="s">
+        <v>357</v>
+      </c>
+      <c r="E118" t="s">
+        <v>357</v>
+      </c>
+      <c r="F118" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="119" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A119" t="s">
+        <v>30</v>
+      </c>
+      <c r="B119" t="s">
+        <v>358</v>
+      </c>
+      <c r="C119" t="s">
+        <v>359</v>
+      </c>
+      <c r="D119" t="s">
+        <v>214</v>
+      </c>
+      <c r="E119" t="s">
+        <v>214</v>
+      </c>
+      <c r="F119" t="s">
+        <v>38</v>
+      </c>
+      <c r="J119" t="s">
+        <v>193</v>
+      </c>
+      <c r="N119" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="120" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A120" t="s">
+        <v>30</v>
+      </c>
+      <c r="B120" t="s">
+        <v>358</v>
+      </c>
+      <c r="C120" t="s">
+        <v>361</v>
+      </c>
+      <c r="D120" t="s">
+        <v>362</v>
+      </c>
+      <c r="E120" t="s">
+        <v>362</v>
+      </c>
+      <c r="F120" t="s">
+        <v>38</v>
+      </c>
+      <c r="J120" t="s">
+        <v>193</v>
+      </c>
+      <c r="N120" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="121" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A121" t="s">
+        <v>30</v>
+      </c>
+      <c r="B121" t="s">
+        <v>358</v>
+      </c>
+      <c r="C121" t="s">
+        <v>363</v>
+      </c>
+      <c r="D121" t="s">
+        <v>364</v>
+      </c>
+      <c r="E121" t="s">
+        <v>364</v>
+      </c>
+      <c r="F121" t="s">
+        <v>38</v>
+      </c>
+      <c r="J121" t="s">
+        <v>193</v>
+      </c>
+      <c r="N121" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="122" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A122" t="s">
+        <v>30</v>
+      </c>
+      <c r="B122" t="s">
+        <v>358</v>
+      </c>
+      <c r="C122" t="s">
+        <v>365</v>
+      </c>
+      <c r="D122" t="s">
+        <v>366</v>
+      </c>
+      <c r="E122" t="s">
+        <v>366</v>
+      </c>
+      <c r="F122" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="123" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A123" t="s">
+        <v>30</v>
+      </c>
+      <c r="B123" t="s">
+        <v>358</v>
+      </c>
+      <c r="C123" t="s">
+        <v>367</v>
+      </c>
+      <c r="D123" t="s">
+        <v>368</v>
+      </c>
+      <c r="E123" t="s">
+        <v>368</v>
+      </c>
+      <c r="F123" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="124" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A124" t="s">
+        <v>30</v>
+      </c>
+      <c r="B124" t="s">
+        <v>369</v>
+      </c>
+      <c r="C124" t="s">
+        <v>370</v>
+      </c>
+      <c r="D124" t="s">
+        <v>371</v>
+      </c>
+      <c r="E124" t="s">
+        <v>371</v>
+      </c>
+      <c r="F124" t="s">
+        <v>38</v>
+      </c>
+      <c r="J124" t="s">
+        <v>372</v>
+      </c>
+      <c r="N124" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="125" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A125" t="s">
+        <v>30</v>
+      </c>
+      <c r="B125" t="s">
+        <v>374</v>
+      </c>
+      <c r="C125" t="s">
+        <v>375</v>
+      </c>
+      <c r="D125" t="s">
+        <v>376</v>
+      </c>
+      <c r="E125" t="s">
+        <v>376</v>
+      </c>
+      <c r="F125" t="s">
+        <v>38</v>
+      </c>
+      <c r="J125" t="s">
+        <v>220</v>
+      </c>
+      <c r="N125" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="126" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A126" t="s">
+        <v>30</v>
+      </c>
+      <c r="B126" t="s">
+        <v>374</v>
+      </c>
+      <c r="C126" t="s">
+        <v>378</v>
+      </c>
+      <c r="D126" t="s">
+        <v>379</v>
+      </c>
+      <c r="E126" t="s">
+        <v>379</v>
+      </c>
+      <c r="F126" t="s">
+        <v>38</v>
+      </c>
+      <c r="J126" t="s">
+        <v>307</v>
+      </c>
+      <c r="N126" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="127" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A127" t="s">
+        <v>30</v>
+      </c>
+      <c r="B127" t="s">
+        <v>374</v>
+      </c>
+      <c r="C127" t="s">
+        <v>380</v>
+      </c>
+      <c r="D127" t="s">
+        <v>381</v>
+      </c>
+      <c r="E127" t="s">
+        <v>381</v>
+      </c>
+      <c r="F127" t="s">
+        <v>38</v>
+      </c>
+      <c r="J127" t="s">
+        <v>307</v>
+      </c>
+      <c r="N127" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="128" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A128" t="s">
+        <v>30</v>
+      </c>
+      <c r="B128" t="s">
+        <v>374</v>
+      </c>
+      <c r="C128" t="s">
+        <v>382</v>
+      </c>
+      <c r="D128" t="s">
+        <v>383</v>
+      </c>
+      <c r="E128" t="s">
+        <v>383</v>
+      </c>
+      <c r="F128" t="s">
+        <v>38</v>
+      </c>
+      <c r="J128" t="s">
+        <v>220</v>
+      </c>
+      <c r="N128" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="129" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A129" t="s">
+        <v>30</v>
+      </c>
+      <c r="B129" t="s">
+        <v>374</v>
+      </c>
+      <c r="C129" t="s">
+        <v>384</v>
+      </c>
+      <c r="D129" t="s">
+        <v>385</v>
+      </c>
+      <c r="E129" t="s">
+        <v>385</v>
+      </c>
+      <c r="F129" t="s">
+        <v>38</v>
+      </c>
+      <c r="J129" t="s">
+        <v>220</v>
+      </c>
+      <c r="N129" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="130" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A130" t="s">
+        <v>30</v>
+      </c>
+      <c r="B130" t="s">
+        <v>374</v>
+      </c>
+      <c r="C130" t="s">
+        <v>386</v>
+      </c>
+      <c r="D130" t="s">
+        <v>387</v>
+      </c>
+      <c r="E130" t="s">
+        <v>387</v>
+      </c>
+      <c r="F130" t="s">
+        <v>38</v>
+      </c>
+      <c r="J130" t="s">
+        <v>220</v>
+      </c>
+      <c r="N130" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="131" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A131" t="s">
+        <v>30</v>
+      </c>
+      <c r="B131" t="s">
+        <v>374</v>
+      </c>
+      <c r="C131" t="s">
+        <v>388</v>
+      </c>
+      <c r="D131" t="s">
+        <v>389</v>
+      </c>
+      <c r="E131" t="s">
+        <v>389</v>
+      </c>
+      <c r="F131" t="s">
+        <v>38</v>
+      </c>
+      <c r="J131" t="s">
+        <v>220</v>
+      </c>
+      <c r="N131" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="132" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A132" t="s">
+        <v>30</v>
+      </c>
+      <c r="B132" t="s">
+        <v>374</v>
+      </c>
+      <c r="C132" t="s">
+        <v>390</v>
+      </c>
+      <c r="D132" t="s">
+        <v>391</v>
+      </c>
+      <c r="E132" t="s">
+        <v>391</v>
+      </c>
+      <c r="F132" t="s">
+        <v>38</v>
+      </c>
+      <c r="J132" t="s">
+        <v>220</v>
+      </c>
+      <c r="N132" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="133" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A133" t="s">
+        <v>30</v>
+      </c>
+      <c r="B133" t="s">
+        <v>374</v>
+      </c>
+      <c r="C133" t="s">
+        <v>392</v>
+      </c>
+      <c r="D133" t="s">
+        <v>393</v>
+      </c>
+      <c r="E133" t="s">
+        <v>393</v>
+      </c>
+      <c r="F133" t="s">
+        <v>38</v>
+      </c>
+      <c r="J133" t="s">
+        <v>220</v>
+      </c>
+      <c r="N133" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="134" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A134" t="s">
+        <v>30</v>
+      </c>
+      <c r="B134" t="s">
+        <v>374</v>
+      </c>
+      <c r="C134" t="s">
+        <v>394</v>
+      </c>
+      <c r="D134" t="s">
+        <v>395</v>
+      </c>
+      <c r="E134" t="s">
+        <v>395</v>
+      </c>
+      <c r="F134" t="s">
+        <v>38</v>
+      </c>
+      <c r="J134" t="s">
+        <v>220</v>
+      </c>
+      <c r="N134" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="135" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A135" t="s">
+        <v>30</v>
+      </c>
+      <c r="B135" t="s">
+        <v>374</v>
+      </c>
+      <c r="C135" t="s">
+        <v>396</v>
+      </c>
+      <c r="D135" t="s">
+        <v>397</v>
+      </c>
+      <c r="E135" t="s">
+        <v>397</v>
+      </c>
+      <c r="F135" t="s">
+        <v>38</v>
+      </c>
+      <c r="J135" t="s">
+        <v>220</v>
+      </c>
+      <c r="N135" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="136" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A136" t="s">
+        <v>30</v>
+      </c>
+      <c r="B136" t="s">
+        <v>374</v>
+      </c>
+      <c r="C136" t="s">
+        <v>398</v>
+      </c>
+      <c r="D136" t="s">
+        <v>399</v>
+      </c>
+      <c r="E136" t="s">
+        <v>399</v>
+      </c>
+      <c r="F136" t="s">
+        <v>38</v>
+      </c>
+      <c r="J136" t="s">
+        <v>220</v>
+      </c>
+      <c r="N136" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="137" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A137" t="s">
+        <v>30</v>
+      </c>
+      <c r="B137" t="s">
+        <v>401</v>
+      </c>
+      <c r="C137" t="s">
+        <v>402</v>
+      </c>
+      <c r="D137" t="s">
+        <v>403</v>
+      </c>
+      <c r="E137" t="s">
+        <v>403</v>
+      </c>
+      <c r="F137" t="s">
+        <v>38</v>
+      </c>
+      <c r="J137" t="s">
+        <v>237</v>
+      </c>
+      <c r="N137" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="138" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A138" t="s">
+        <v>30</v>
+      </c>
+      <c r="B138" t="s">
+        <v>401</v>
+      </c>
+      <c r="C138" t="s">
+        <v>405</v>
+      </c>
+      <c r="D138" t="s">
+        <v>406</v>
+      </c>
+      <c r="E138" t="s">
+        <v>406</v>
+      </c>
+      <c r="F138" t="s">
+        <v>38</v>
+      </c>
+      <c r="J138" t="s">
+        <v>237</v>
+      </c>
+      <c r="N138" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="139" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A139" t="s">
+        <v>30</v>
+      </c>
+      <c r="B139" t="s">
+        <v>401</v>
+      </c>
+      <c r="C139" t="s">
+        <v>407</v>
+      </c>
+      <c r="D139" t="s">
+        <v>408</v>
+      </c>
+      <c r="E139" t="s">
+        <v>408</v>
+      </c>
+      <c r="F139" t="s">
+        <v>38</v>
+      </c>
+      <c r="J139" t="s">
+        <v>237</v>
+      </c>
+      <c r="N139" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="140" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A140" t="s">
+        <v>30</v>
+      </c>
+      <c r="B140" t="s">
+        <v>401</v>
+      </c>
+      <c r="C140" t="s">
+        <v>409</v>
+      </c>
+      <c r="D140" t="s">
+        <v>410</v>
+      </c>
+      <c r="E140" t="s">
+        <v>410</v>
+      </c>
+      <c r="F140" t="s">
+        <v>38</v>
+      </c>
+      <c r="J140" t="s">
+        <v>237</v>
+      </c>
+      <c r="N140" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="141" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A141" t="s">
+        <v>30</v>
+      </c>
+      <c r="B141" t="s">
+        <v>401</v>
+      </c>
+      <c r="C141" t="s">
+        <v>411</v>
+      </c>
+      <c r="D141" t="s">
+        <v>412</v>
+      </c>
+      <c r="E141" t="s">
+        <v>412</v>
+      </c>
+      <c r="F141" t="s">
+        <v>38</v>
+      </c>
+      <c r="J141" t="s">
+        <v>60</v>
+      </c>
+      <c r="N141" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="142" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A142" t="s">
+        <v>30</v>
+      </c>
+      <c r="B142" t="s">
+        <v>401</v>
+      </c>
+      <c r="C142" t="s">
+        <v>413</v>
+      </c>
+      <c r="D142" t="s">
+        <v>414</v>
+      </c>
+      <c r="E142" t="s">
+        <v>414</v>
+      </c>
+      <c r="F142" t="s">
+        <v>38</v>
+      </c>
+      <c r="J142" t="s">
+        <v>60</v>
+      </c>
+      <c r="N142" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="143" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A143" t="s">
+        <v>30</v>
+      </c>
+      <c r="B143" t="s">
+        <v>401</v>
+      </c>
+      <c r="C143" t="s">
+        <v>415</v>
+      </c>
+      <c r="D143" t="s">
+        <v>416</v>
+      </c>
+      <c r="E143" t="s">
+        <v>416</v>
+      </c>
+      <c r="F143" t="s">
+        <v>38</v>
+      </c>
+      <c r="J143" t="s">
+        <v>60</v>
+      </c>
+      <c r="N143" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="144" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A144" t="s">
+        <v>30</v>
+      </c>
+      <c r="B144" t="s">
+        <v>401</v>
+      </c>
+      <c r="C144" t="s">
+        <v>417</v>
+      </c>
+      <c r="D144" t="s">
+        <v>418</v>
+      </c>
+      <c r="E144" t="s">
+        <v>418</v>
+      </c>
+      <c r="F144" t="s">
+        <v>38</v>
+      </c>
+      <c r="J144" t="s">
+        <v>60</v>
+      </c>
+      <c r="N144" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="145" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A145" t="s">
+        <v>30</v>
+      </c>
+      <c r="B145" t="s">
+        <v>401</v>
+      </c>
+      <c r="C145" t="s">
+        <v>419</v>
+      </c>
+      <c r="D145" t="s">
+        <v>420</v>
+      </c>
+      <c r="E145" t="s">
+        <v>420</v>
+      </c>
+      <c r="F145" t="s">
+        <v>38</v>
+      </c>
+      <c r="J145" t="s">
+        <v>60</v>
+      </c>
+      <c r="N145" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="146" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A146" t="s">
+        <v>30</v>
+      </c>
+      <c r="B146" t="s">
+        <v>401</v>
+      </c>
+      <c r="C146" t="s">
+        <v>421</v>
+      </c>
+      <c r="D146" t="s">
+        <v>422</v>
+      </c>
+      <c r="E146" t="s">
+        <v>422</v>
+      </c>
+      <c r="F146" t="s">
+        <v>38</v>
+      </c>
+      <c r="J146" t="s">
+        <v>60</v>
+      </c>
+      <c r="N146" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="147" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A147" t="s">
+        <v>30</v>
+      </c>
+      <c r="B147" t="s">
+        <v>401</v>
+      </c>
+      <c r="C147" t="s">
+        <v>423</v>
+      </c>
+      <c r="D147" t="s">
+        <v>424</v>
+      </c>
+      <c r="E147" t="s">
+        <v>424</v>
+      </c>
+      <c r="F147" t="s">
+        <v>38</v>
+      </c>
+      <c r="J147" t="s">
+        <v>60</v>
+      </c>
+      <c r="N147" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="148" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A148" t="s">
+        <v>30</v>
+      </c>
+      <c r="B148" t="s">
+        <v>401</v>
+      </c>
+      <c r="C148" t="s">
+        <v>425</v>
+      </c>
+      <c r="D148" t="s">
+        <v>426</v>
+      </c>
+      <c r="E148" t="s">
+        <v>426</v>
+      </c>
+      <c r="F148" t="s">
+        <v>38</v>
+      </c>
+      <c r="J148" t="s">
+        <v>60</v>
+      </c>
+      <c r="N148" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="149" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A149" t="s">
+        <v>30</v>
+      </c>
+      <c r="B149" t="s">
+        <v>401</v>
+      </c>
+      <c r="C149" t="s">
+        <v>427</v>
+      </c>
+      <c r="D149" t="s">
+        <v>428</v>
+      </c>
+      <c r="E149" t="s">
+        <v>428</v>
+      </c>
+      <c r="F149" t="s">
+        <v>38</v>
+      </c>
+      <c r="J149" t="s">
+        <v>60</v>
+      </c>
+      <c r="N149" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="150" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A150" t="s">
+        <v>30</v>
+      </c>
+      <c r="B150" t="s">
+        <v>401</v>
+      </c>
+      <c r="C150" t="s">
+        <v>429</v>
+      </c>
+      <c r="D150" t="s">
+        <v>430</v>
+      </c>
+      <c r="E150" t="s">
+        <v>430</v>
+      </c>
+      <c r="F150" t="s">
+        <v>38</v>
+      </c>
+      <c r="J150" t="s">
+        <v>60</v>
+      </c>
+      <c r="N150" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="151" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A151" t="s">
+        <v>30</v>
+      </c>
+      <c r="B151" t="s">
+        <v>401</v>
+      </c>
+      <c r="C151" t="s">
+        <v>431</v>
+      </c>
+      <c r="D151" t="s">
+        <v>432</v>
+      </c>
+      <c r="E151" t="s">
+        <v>432</v>
+      </c>
+      <c r="F151" t="s">
+        <v>38</v>
+      </c>
+      <c r="J151" t="s">
+        <v>60</v>
+      </c>
+      <c r="N151" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="152" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A152" t="s">
+        <v>30</v>
+      </c>
+      <c r="B152" t="s">
+        <v>401</v>
+      </c>
+      <c r="C152" t="s">
+        <v>433</v>
+      </c>
+      <c r="D152" t="s">
+        <v>434</v>
+      </c>
+      <c r="E152" t="s">
+        <v>434</v>
+      </c>
+      <c r="F152" t="s">
+        <v>38</v>
+      </c>
+      <c r="J152" t="s">
+        <v>60</v>
+      </c>
+      <c r="N152" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="153" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A153" t="s">
+        <v>30</v>
+      </c>
+      <c r="B153" t="s">
+        <v>401</v>
+      </c>
+      <c r="C153" t="s">
+        <v>435</v>
+      </c>
+      <c r="D153" t="s">
+        <v>436</v>
+      </c>
+      <c r="E153" t="s">
+        <v>436</v>
+      </c>
+      <c r="F153" t="s">
+        <v>38</v>
+      </c>
+      <c r="J153" t="s">
+        <v>60</v>
+      </c>
+      <c r="N153" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="154" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A154" t="s">
+        <v>30</v>
+      </c>
+      <c r="B154" t="s">
+        <v>401</v>
+      </c>
+      <c r="C154" t="s">
+        <v>437</v>
+      </c>
+      <c r="D154" t="s">
+        <v>438</v>
+      </c>
+      <c r="E154" t="s">
+        <v>438</v>
+      </c>
+      <c r="F154" t="s">
+        <v>38</v>
+      </c>
+      <c r="J154" t="s">
+        <v>60</v>
+      </c>
+      <c r="N154" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="155" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A155" t="s">
+        <v>30</v>
+      </c>
+      <c r="B155" t="s">
+        <v>401</v>
+      </c>
+      <c r="C155" t="s">
+        <v>439</v>
+      </c>
+      <c r="D155" t="s">
+        <v>440</v>
+      </c>
+      <c r="E155" t="s">
+        <v>440</v>
+      </c>
+      <c r="F155" t="s">
+        <v>38</v>
+      </c>
+      <c r="J155" t="s">
+        <v>60</v>
+      </c>
+      <c r="N155" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="156" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A156" t="s">
+        <v>30</v>
+      </c>
+      <c r="B156" t="s">
+        <v>401</v>
+      </c>
+      <c r="C156" t="s">
+        <v>441</v>
+      </c>
+      <c r="D156" t="s">
+        <v>442</v>
+      </c>
+      <c r="E156" t="s">
+        <v>442</v>
+      </c>
+      <c r="F156" t="s">
+        <v>38</v>
+      </c>
+      <c r="J156" t="s">
+        <v>60</v>
+      </c>
+      <c r="N156" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="157" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A157" t="s">
+        <v>30</v>
+      </c>
+      <c r="B157" t="s">
+        <v>401</v>
+      </c>
+      <c r="C157" t="s">
+        <v>443</v>
+      </c>
+      <c r="D157" t="s">
+        <v>444</v>
+      </c>
+      <c r="E157" t="s">
+        <v>444</v>
+      </c>
+      <c r="F157" t="s">
+        <v>38</v>
+      </c>
+      <c r="J157" t="s">
+        <v>60</v>
+      </c>
+      <c r="N157" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="158" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A158" t="s">
+        <v>30</v>
+      </c>
+      <c r="B158" t="s">
+        <v>401</v>
+      </c>
+      <c r="C158" t="s">
+        <v>445</v>
+      </c>
+      <c r="D158" t="s">
+        <v>446</v>
+      </c>
+      <c r="E158" t="s">
+        <v>446</v>
+      </c>
+      <c r="F158" t="s">
+        <v>38</v>
+      </c>
+      <c r="J158" t="s">
+        <v>60</v>
+      </c>
+      <c r="N158" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="159" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A159" t="s">
+        <v>30</v>
+      </c>
+      <c r="B159" t="s">
+        <v>401</v>
+      </c>
+      <c r="C159" t="s">
+        <v>447</v>
+      </c>
+      <c r="D159" t="s">
+        <v>448</v>
+      </c>
+      <c r="E159" t="s">
+        <v>448</v>
+      </c>
+      <c r="F159" t="s">
+        <v>38</v>
+      </c>
+      <c r="J159" t="s">
+        <v>60</v>
+      </c>
+      <c r="N159" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="160" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A160" t="s">
+        <v>30</v>
+      </c>
+      <c r="B160" t="s">
+        <v>401</v>
+      </c>
+      <c r="C160" t="s">
+        <v>449</v>
+      </c>
+      <c r="D160" t="s">
+        <v>450</v>
+      </c>
+      <c r="E160" t="s">
+        <v>450</v>
+      </c>
+      <c r="F160" t="s">
+        <v>38</v>
+      </c>
+      <c r="J160" t="s">
+        <v>60</v>
+      </c>
+      <c r="N160" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="161" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A161" t="s">
+        <v>30</v>
+      </c>
+      <c r="B161" t="s">
+        <v>401</v>
+      </c>
+      <c r="C161" t="s">
+        <v>451</v>
+      </c>
+      <c r="D161" t="s">
+        <v>452</v>
+      </c>
+      <c r="E161" t="s">
+        <v>452</v>
+      </c>
+      <c r="F161" t="s">
+        <v>38</v>
+      </c>
+      <c r="J161" t="s">
+        <v>60</v>
+      </c>
+      <c r="N161" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="162" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A162" t="s">
+        <v>30</v>
+      </c>
+      <c r="B162" t="s">
+        <v>401</v>
+      </c>
+      <c r="C162" t="s">
+        <v>453</v>
+      </c>
+      <c r="D162" t="s">
+        <v>454</v>
+      </c>
+      <c r="E162" t="s">
+        <v>454</v>
+      </c>
+      <c r="F162" t="s">
+        <v>38</v>
+      </c>
+      <c r="J162" t="s">
+        <v>60</v>
+      </c>
+      <c r="N162" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="163" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A163" t="s">
+        <v>30</v>
+      </c>
+      <c r="B163" t="s">
+        <v>401</v>
+      </c>
+      <c r="C163" t="s">
+        <v>455</v>
+      </c>
+      <c r="D163" t="s">
+        <v>456</v>
+      </c>
+      <c r="E163" t="s">
+        <v>456</v>
+      </c>
+      <c r="F163" t="s">
+        <v>38</v>
+      </c>
+      <c r="J163" t="s">
+        <v>60</v>
+      </c>
+      <c r="N163" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="164" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A164" t="s">
+        <v>30</v>
+      </c>
+      <c r="B164" t="s">
+        <v>401</v>
+      </c>
+      <c r="C164" t="s">
+        <v>457</v>
+      </c>
+      <c r="D164" t="s">
+        <v>458</v>
+      </c>
+      <c r="E164" t="s">
+        <v>458</v>
+      </c>
+      <c r="F164" t="s">
+        <v>38</v>
+      </c>
+      <c r="J164" t="s">
+        <v>60</v>
+      </c>
+      <c r="N164" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="165" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A165" t="s">
+        <v>30</v>
+      </c>
+      <c r="B165" t="s">
+        <v>401</v>
+      </c>
+      <c r="C165" t="s">
+        <v>459</v>
+      </c>
+      <c r="D165" t="s">
+        <v>460</v>
+      </c>
+      <c r="E165" t="s">
+        <v>460</v>
+      </c>
+      <c r="F165" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="166" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A166" t="s">
+        <v>30</v>
+      </c>
+      <c r="B166" t="s">
+        <v>401</v>
+      </c>
+      <c r="C166" t="s">
+        <v>461</v>
+      </c>
+      <c r="D166" t="s">
+        <v>460</v>
+      </c>
+      <c r="E166" t="s">
+        <v>460</v>
+      </c>
+      <c r="F166" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="167" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A167" t="s">
+        <v>30</v>
+      </c>
+      <c r="B167" t="s">
+        <v>401</v>
+      </c>
+      <c r="C167" t="s">
+        <v>462</v>
+      </c>
+      <c r="D167" t="s">
+        <v>460</v>
+      </c>
+      <c r="E167" t="s">
+        <v>460</v>
+      </c>
+      <c r="F167" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="168" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A168" t="s">
+        <v>30</v>
+      </c>
+      <c r="B168" t="s">
+        <v>401</v>
+      </c>
+      <c r="C168" t="s">
+        <v>463</v>
+      </c>
+      <c r="D168" t="s">
+        <v>460</v>
+      </c>
+      <c r="E168" t="s">
+        <v>460</v>
+      </c>
+      <c r="F168" t="s">
+        <v>44</v>
       </c>
     </row>
   </sheetData>

--- a/CDE_ID_detective_revamp/in/Testfile.xlsx
+++ b/CDE_ID_detective_revamp/in/Testfile.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lmaefos\Code Stuffs\CDE_detective\CDE_ID_detective_revamp\in\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{74A45D79-AD2C-43B2-9762-8753FB6771C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9041BD5D-201C-41D4-A753-1309F3A61AFD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-30750" yWindow="7230" windowWidth="25830" windowHeight="15105" xr2:uid="{B4172F7E-1829-43FF-A6F3-7109D1C548C2}"/>
+    <workbookView xWindow="-38520" yWindow="4380" windowWidth="38640" windowHeight="21120" xr2:uid="{B4172F7E-1829-43FF-A6F3-7109D1C548C2}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -161,42 +161,21 @@
     <t>0|1|2|3|4|5|6|7|8|9|10</t>
   </si>
   <si>
-    <t>bpisev</t>
-  </si>
-  <si>
-    <t>BPIWrstPnLast24HRtngScl</t>
-  </si>
-  <si>
     <t>Worst Pain in the Last 24 Hours</t>
   </si>
   <si>
     <t>0=No pain (0)|1=1|2=2|3=3|4=4|5=5|6=6|7=7|8=8|9=9|10=Pain as bad as you can imagine (10)</t>
   </si>
   <si>
-    <t>BPILeastPnLst24HRtngScl</t>
-  </si>
-  <si>
     <t>Least Pain in the Last 24 Hours</t>
   </si>
   <si>
-    <t>BPIAvgPainRtngScl</t>
-  </si>
-  <si>
     <t>Average Pain</t>
   </si>
   <si>
-    <t>BPICurrentPainRtngScl</t>
-  </si>
-  <si>
     <t>Current Pain</t>
   </si>
   <si>
-    <t>gad7</t>
-  </si>
-  <si>
-    <t>GAD2FeelNervScl</t>
-  </si>
-  <si>
     <t>Feeling Nervous</t>
   </si>
   <si>
@@ -206,47 +185,68 @@
     <t>0=Not at all|1=Several Days|2=More than half the days|3=Nearly every day</t>
   </si>
   <si>
-    <t>GAD2NotStopWryScl</t>
-  </si>
-  <si>
     <t>Unable to Stop Worrying</t>
   </si>
   <si>
-    <t>GAD7WryTooMchScl</t>
-  </si>
-  <si>
     <t>Worrying Too Much</t>
   </si>
   <si>
-    <t>GAD7TroubRelxScl</t>
-  </si>
-  <si>
     <t>Trouble Relaxing</t>
   </si>
   <si>
-    <t>GAD7RstlessScl</t>
-  </si>
-  <si>
     <t>Being Restless</t>
   </si>
   <si>
-    <t>GAD7EasyAnnoyedScl</t>
-  </si>
-  <si>
     <t>Becoming Easily Annoyed/Irritable</t>
   </si>
   <si>
-    <t>GAD7FeelAfrdScl</t>
-  </si>
-  <si>
     <t>Feeling Afraid</t>
+  </si>
+  <si>
+    <t>FORM1</t>
+  </si>
+  <si>
+    <t>FORM2</t>
+  </si>
+  <si>
+    <t>AvgPainRtngScl</t>
+  </si>
+  <si>
+    <t>CurrentPainRtngScl</t>
+  </si>
+  <si>
+    <t>LeastPnLst24HRtngScl</t>
+  </si>
+  <si>
+    <t>WrstPnLast24HRtngScl</t>
+  </si>
+  <si>
+    <t>FeelNervScl</t>
+  </si>
+  <si>
+    <t>NotStopWryScl</t>
+  </si>
+  <si>
+    <t>EasyAnnoyedScl</t>
+  </si>
+  <si>
+    <t>FeelAfrdScl</t>
+  </si>
+  <si>
+    <t>RstlessScl</t>
+  </si>
+  <si>
+    <t>TroubRelxScl</t>
+  </si>
+  <si>
+    <t>WryTooMchScl</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="18" x14ac:knownFonts="1">
+  <fonts count="19" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -377,6 +377,12 @@
     <font>
       <sz val="11"/>
       <color theme="0"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -1104,6 +1110,7 @@
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="2" max="2" width="33.19921875" customWidth="1"/>
+    <col min="3" max="3" width="18" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:30" x14ac:dyDescent="0.45">
@@ -1263,16 +1270,16 @@
         <v>30</v>
       </c>
       <c r="B5" t="s">
-        <v>41</v>
+        <v>55</v>
       </c>
       <c r="C5" t="s">
-        <v>47</v>
+        <v>57</v>
       </c>
       <c r="D5" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="E5" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="F5" t="s">
         <v>31</v>
@@ -1281,7 +1288,7 @@
         <v>40</v>
       </c>
       <c r="N5" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
     </row>
     <row r="6" spans="1:30" x14ac:dyDescent="0.45">
@@ -1289,16 +1296,16 @@
         <v>30</v>
       </c>
       <c r="B6" t="s">
-        <v>41</v>
+        <v>55</v>
       </c>
       <c r="C6" t="s">
-        <v>49</v>
+        <v>58</v>
       </c>
       <c r="D6" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="E6" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="F6" t="s">
         <v>31</v>
@@ -1307,7 +1314,7 @@
         <v>40</v>
       </c>
       <c r="N6" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
     </row>
     <row r="7" spans="1:30" x14ac:dyDescent="0.45">
@@ -1315,16 +1322,16 @@
         <v>30</v>
       </c>
       <c r="B7" t="s">
-        <v>41</v>
+        <v>55</v>
       </c>
       <c r="C7" t="s">
-        <v>45</v>
+        <v>59</v>
       </c>
       <c r="D7" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="E7" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="F7" t="s">
         <v>31</v>
@@ -1333,7 +1340,7 @@
         <v>40</v>
       </c>
       <c r="N7" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
     </row>
     <row r="8" spans="1:30" x14ac:dyDescent="0.45">
@@ -1341,16 +1348,16 @@
         <v>30</v>
       </c>
       <c r="B8" t="s">
+        <v>55</v>
+      </c>
+      <c r="C8" t="s">
+        <v>60</v>
+      </c>
+      <c r="D8" t="s">
         <v>41</v>
       </c>
-      <c r="C8" t="s">
-        <v>42</v>
-      </c>
-      <c r="D8" t="s">
-        <v>43</v>
-      </c>
       <c r="E8" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="F8" t="s">
         <v>31</v>
@@ -1359,7 +1366,7 @@
         <v>40</v>
       </c>
       <c r="N8" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
     </row>
     <row r="9" spans="1:30" x14ac:dyDescent="0.45">
@@ -1367,25 +1374,25 @@
         <v>30</v>
       </c>
       <c r="B9" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="C9" t="s">
-        <v>52</v>
+        <v>61</v>
       </c>
       <c r="D9" t="s">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="E9" t="s">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="F9" t="s">
         <v>31</v>
       </c>
       <c r="J9" t="s">
-        <v>54</v>
+        <v>47</v>
       </c>
       <c r="N9" t="s">
-        <v>55</v>
+        <v>48</v>
       </c>
     </row>
     <row r="10" spans="1:30" x14ac:dyDescent="0.45">
@@ -1393,25 +1400,25 @@
         <v>30</v>
       </c>
       <c r="B10" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="C10" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="D10" t="s">
-        <v>57</v>
+        <v>49</v>
       </c>
       <c r="E10" t="s">
-        <v>57</v>
+        <v>49</v>
       </c>
       <c r="F10" t="s">
         <v>31</v>
       </c>
       <c r="J10" t="s">
-        <v>54</v>
+        <v>47</v>
       </c>
       <c r="N10" t="s">
-        <v>55</v>
+        <v>48</v>
       </c>
     </row>
     <row r="11" spans="1:30" x14ac:dyDescent="0.45">
@@ -1419,25 +1426,25 @@
         <v>30</v>
       </c>
       <c r="B11" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="C11" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D11" t="s">
-        <v>65</v>
+        <v>53</v>
       </c>
       <c r="E11" t="s">
-        <v>65</v>
+        <v>53</v>
       </c>
       <c r="F11" t="s">
         <v>31</v>
       </c>
       <c r="J11" t="s">
-        <v>54</v>
+        <v>47</v>
       </c>
       <c r="N11" t="s">
-        <v>55</v>
+        <v>48</v>
       </c>
     </row>
     <row r="12" spans="1:30" x14ac:dyDescent="0.45">
@@ -1445,25 +1452,25 @@
         <v>30</v>
       </c>
       <c r="B12" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="C12" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="D12" t="s">
-        <v>67</v>
+        <v>54</v>
       </c>
       <c r="E12" t="s">
-        <v>67</v>
+        <v>54</v>
       </c>
       <c r="F12" t="s">
         <v>31</v>
       </c>
       <c r="J12" t="s">
-        <v>54</v>
+        <v>47</v>
       </c>
       <c r="N12" t="s">
-        <v>55</v>
+        <v>48</v>
       </c>
     </row>
     <row r="13" spans="1:30" x14ac:dyDescent="0.45">
@@ -1471,25 +1478,25 @@
         <v>30</v>
       </c>
       <c r="B13" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="C13" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="D13" t="s">
-        <v>63</v>
+        <v>52</v>
       </c>
       <c r="E13" t="s">
-        <v>63</v>
+        <v>52</v>
       </c>
       <c r="F13" t="s">
         <v>31</v>
       </c>
       <c r="J13" t="s">
-        <v>54</v>
+        <v>47</v>
       </c>
       <c r="N13" t="s">
-        <v>55</v>
+        <v>48</v>
       </c>
     </row>
     <row r="14" spans="1:30" x14ac:dyDescent="0.45">
@@ -1497,25 +1504,25 @@
         <v>30</v>
       </c>
       <c r="B14" t="s">
+        <v>56</v>
+      </c>
+      <c r="C14" t="s">
+        <v>66</v>
+      </c>
+      <c r="D14" t="s">
         <v>51</v>
       </c>
-      <c r="C14" t="s">
-        <v>60</v>
-      </c>
-      <c r="D14" t="s">
-        <v>61</v>
-      </c>
       <c r="E14" t="s">
-        <v>61</v>
+        <v>51</v>
       </c>
       <c r="F14" t="s">
         <v>31</v>
       </c>
       <c r="J14" t="s">
-        <v>54</v>
+        <v>47</v>
       </c>
       <c r="N14" t="s">
-        <v>55</v>
+        <v>48</v>
       </c>
     </row>
     <row r="15" spans="1:30" x14ac:dyDescent="0.45">
@@ -1523,25 +1530,25 @@
         <v>30</v>
       </c>
       <c r="B15" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="C15" t="s">
-        <v>58</v>
+        <v>67</v>
       </c>
       <c r="D15" t="s">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="E15" t="s">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="F15" t="s">
         <v>31</v>
       </c>
       <c r="J15" t="s">
-        <v>54</v>
+        <v>47</v>
       </c>
       <c r="N15" t="s">
-        <v>55</v>
+        <v>48</v>
       </c>
     </row>
   </sheetData>
@@ -1550,6 +1557,7 @@
       <sortCondition ref="B1:B15"/>
     </sortState>
   </autoFilter>
+  <phoneticPr fontId="18" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/CDE_ID_detective_revamp/in/Testfile.xlsx
+++ b/CDE_ID_detective_revamp/in/Testfile.xlsx
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lmaefos\Code Stuffs\CDE_detective\CDE_ID_detective_revamp\in\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9041BD5D-201C-41D4-A753-1309F3A61AFD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{817B149D-0F69-43F3-8A18-7056A50B2854}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-38520" yWindow="4380" windowWidth="38640" windowHeight="21120" xr2:uid="{B4172F7E-1829-43FF-A6F3-7109D1C548C2}"/>
+    <workbookView xWindow="-19305" yWindow="4500" windowWidth="19410" windowHeight="20985" xr2:uid="{B4172F7E-1829-43FF-A6F3-7109D1C548C2}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$AD$15</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$AC$15</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,10 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="68">
-  <si>
-    <t>schemaVersion</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="281" uniqueCount="172">
   <si>
     <t>section</t>
   </si>
@@ -128,9 +125,6 @@
     <t>relatedConcepts[0].id</t>
   </si>
   <si>
-    <t>0.3.2</t>
-  </si>
-  <si>
     <t>integer</t>
   </si>
   <si>
@@ -240,6 +234,324 @@
   </si>
   <si>
     <t>WryTooMchScl</t>
+  </si>
+  <si>
+    <t>FORM3</t>
+  </si>
+  <si>
+    <t>subject_id</t>
+  </si>
+  <si>
+    <t>visit</t>
+  </si>
+  <si>
+    <t>tobaccoproductscl</t>
+  </si>
+  <si>
+    <t>alcoholusemalescl</t>
+  </si>
+  <si>
+    <t>alcoholusefemalescl</t>
+  </si>
+  <si>
+    <t>drugusescl</t>
+  </si>
+  <si>
+    <t>prescriptionmedusescl</t>
+  </si>
+  <si>
+    <t>overallyn</t>
+  </si>
+  <si>
+    <t>Subject ID</t>
+  </si>
+  <si>
+    <t>Study Visit</t>
+  </si>
+  <si>
+    <t>have you used any tobacco product (for example, cigarettes, e-cigarettes, cigars, pipes, or smokeless tobacco)?</t>
+  </si>
+  <si>
+    <t>how often have you had 5 or more drinks containing alcohol in one day? One standard drink is about 1 small glass of wine (5 oz), 1 beer (12 oz), or 1 single shot of liquor.</t>
+  </si>
+  <si>
+    <t>how often have you had 4 or more drinks containing alcohol in one day? One standard drink is about 1 small glass of wine (5 oz), 1 beer (12 oz), or 1 single shot of liquor.</t>
+  </si>
+  <si>
+    <t>have you used any drugs including marijuana, cocaine or crack,heroin, methamphetamine (crystal meth), hallucinogens, ecstasy/MDMA?</t>
+  </si>
+  <si>
+    <t>have you used any prescription medications just for the feeling, more than prescribed or that were not prescribed for you? Prescription medications that may be used this way include: Opiate pain relievers (for example, OxyContin, Vicodin, Percocet, Methadone) Medications for anxiety or sleeping (for example, Xanax, Ativan, Klonopin) Medications for ADHD (for example, Adderall or Ritalin)?</t>
+  </si>
+  <si>
+    <t>Overall TAPS part 1</t>
+  </si>
+  <si>
+    <t>1,Visit 1 | 2,Visit 2</t>
+  </si>
+  <si>
+    <t>0,Daily or Almost Daily | 1,Weekly | 2,Monthly | 3,Less Than Monthly | 4,Never</t>
+  </si>
+  <si>
+    <t>sum([tapstobaccoproductscl], [tapsalcoholusemalescl], [tapsalcoholusefemalescl], [tapsdrugusescl], [tapsprescriptionmedusescl] &gt; 1, 1, 0)</t>
+  </si>
+  <si>
+    <t>brthdtc</t>
+  </si>
+  <si>
+    <t>age</t>
+  </si>
+  <si>
+    <t>sex</t>
+  </si>
+  <si>
+    <t>genident</t>
+  </si>
+  <si>
+    <t>ethnic</t>
+  </si>
+  <si>
+    <t>race___1</t>
+  </si>
+  <si>
+    <t>race___2</t>
+  </si>
+  <si>
+    <t>race___3</t>
+  </si>
+  <si>
+    <t>race___4</t>
+  </si>
+  <si>
+    <t>race___5</t>
+  </si>
+  <si>
+    <t>race___6</t>
+  </si>
+  <si>
+    <t>race___7</t>
+  </si>
+  <si>
+    <t>edlevel</t>
+  </si>
+  <si>
+    <t>empstat</t>
+  </si>
+  <si>
+    <t>maristat</t>
+  </si>
+  <si>
+    <t>hhnum</t>
+  </si>
+  <si>
+    <t>paindur</t>
+  </si>
+  <si>
+    <t>baseline_demographics</t>
+  </si>
+  <si>
+    <t>Date of Birth: (mm/dd/yyyy)</t>
+  </si>
+  <si>
+    <t>Age:</t>
+  </si>
+  <si>
+    <t>Sex at birth:</t>
+  </si>
+  <si>
+    <t>Gender Identity:</t>
+  </si>
+  <si>
+    <t>Ethnicity: (Choose one)</t>
+  </si>
+  <si>
+    <t>Race: American Indian or Alaskan Native</t>
+  </si>
+  <si>
+    <t>Race: Asian</t>
+  </si>
+  <si>
+    <t>Race: Black or African American</t>
+  </si>
+  <si>
+    <t>Race: Native Hawaiian or Pacific Islander</t>
+  </si>
+  <si>
+    <t>Race: White</t>
+  </si>
+  <si>
+    <t>Race: Unknown</t>
+  </si>
+  <si>
+    <t>Race: Not reported</t>
+  </si>
+  <si>
+    <t>What is the highest level of education you have completed?</t>
+  </si>
+  <si>
+    <t>What is your current employment status?</t>
+  </si>
+  <si>
+    <t>What category best describes your current relationship status?</t>
+  </si>
+  <si>
+    <t>Including yourself, how many people live in your household?</t>
+  </si>
+  <si>
+    <t>How long have you had the type of pain for which you are enrolled in this study? (Please list the number of months)</t>
+  </si>
+  <si>
+    <t>Part of the Minimal Dataset: Date of Birth: (mm/dd/yyyy)</t>
+  </si>
+  <si>
+    <t>Part of the Minimal Dataset: Age:</t>
+  </si>
+  <si>
+    <t>Part of the Minimal Dataset: Sex at birth:</t>
+  </si>
+  <si>
+    <t>Part of the Minimal Dataset: Gender Identity:</t>
+  </si>
+  <si>
+    <t>Part of the Minimal Dataset: Ethnicity: (Choose one)</t>
+  </si>
+  <si>
+    <t>Part of the Minimal Dataset: Race: (Choose all that apply)[choice=American Indian or Alaskan Native]</t>
+  </si>
+  <si>
+    <t>Part of the Minimal Dataset: Race: (Choose all that apply)[choice=Asian]</t>
+  </si>
+  <si>
+    <t>Part of the Minimal Dataset: Race: (Choose all that apply)[choice=Black or African American]</t>
+  </si>
+  <si>
+    <t>Part of the Minimal Dataset: Race: (Choose all that apply)[choice=Native Hawaiian or Pacific Islander]</t>
+  </si>
+  <si>
+    <t>Part of the Minimal Dataset: Race: (Choose all that apply)[choice=White]</t>
+  </si>
+  <si>
+    <t>Part of the Minimal Dataset: Race: (Choose all that apply)[choice=Unknown]</t>
+  </si>
+  <si>
+    <t>Part of the Minimal Dataset: Race: (Choose all that apply)[choice=Not reported]</t>
+  </si>
+  <si>
+    <t>Part of the Minimal Dataset: What is the highest level of education you have completed?</t>
+  </si>
+  <si>
+    <t>Part of the Minimal Dataset: What is your current employment status?</t>
+  </si>
+  <si>
+    <t>Part of the Minimal Dataset: What category best describes your current relationship status?</t>
+  </si>
+  <si>
+    <t>Part of the Minimal Dataset: Including yourself, how many people live in your household?</t>
+  </si>
+  <si>
+    <t>Part of the Minimal Dataset: How long have you had the type of pain for which you are enrolled in this study? (Please list the number of months)</t>
+  </si>
+  <si>
+    <t>1|2|3|4</t>
+  </si>
+  <si>
+    <t>0|1</t>
+  </si>
+  <si>
+    <t>1|2|3|4|5|6|7|8|9</t>
+  </si>
+  <si>
+    <t>1|2|3|4|5</t>
+  </si>
+  <si>
+    <t>1=Male|2=Female|3=Unknown|4=Intersex</t>
+  </si>
+  <si>
+    <t>1=Male|2=Female|3=Unknown|4=Other, specify, [Open Text]</t>
+  </si>
+  <si>
+    <t>1=Hispanic or Latino|2=Not Hispanic or Latino|3=Unknown|4=Not reported</t>
+  </si>
+  <si>
+    <t>0=Unchecked|1=Checked</t>
+  </si>
+  <si>
+    <t>1=Primary (Elementary School)|2=Lower Secondary (Middle School)|3=Upper Secondary (High School)|4=Diploma or equivalent (GED)|5=Some college/Certificate|6=Vocation/Trade School|7=Bachelor’s Degree|8=Some Graduate or Professional School|9=Graduate or Professional School diploma</t>
+  </si>
+  <si>
+    <t>1=Full-time employment|2=Not employed|3=Part-time employment|4=Retired</t>
+  </si>
+  <si>
+    <t>1=Divorced|2=Married|3=Never married|4=Separated|5=Widowed</t>
+  </si>
+  <si>
+    <t>fibromyalgia_fm_survey_criteria_2016</t>
+  </si>
+  <si>
+    <t>face</t>
+  </si>
+  <si>
+    <t>Face</t>
+  </si>
+  <si>
+    <t>Widespread Pain Index (WPI) and Symptom Severity Index (SSI): Face</t>
+  </si>
+  <si>
+    <t>rt_jaw</t>
+  </si>
+  <si>
+    <t>Rt Jaw</t>
+  </si>
+  <si>
+    <t>Widespread Pain Index (WPI) and Symptom Severity Index (SSI): Rt Jaw</t>
+  </si>
+  <si>
+    <t>lt_jaw</t>
+  </si>
+  <si>
+    <t>Lt Jaw</t>
+  </si>
+  <si>
+    <t>Widespread Pain Index (WPI) and Symptom Severity Index (SSI): Lt Jaw</t>
+  </si>
+  <si>
+    <t>rt_breast</t>
+  </si>
+  <si>
+    <t>Rt Breast</t>
+  </si>
+  <si>
+    <t>Widespread Pain Index (WPI) and Symptom Severity Index (SSI): Rt Breast</t>
+  </si>
+  <si>
+    <t>lt_breast</t>
+  </si>
+  <si>
+    <t>Lt Breast</t>
+  </si>
+  <si>
+    <t>Widespread Pain Index (WPI) and Symptom Severity Index (SSI): Lt Breast</t>
+  </si>
+  <si>
+    <t>rt_upper_arm</t>
+  </si>
+  <si>
+    <t>Rt upper arm</t>
+  </si>
+  <si>
+    <t>Widespread Pain Index (WPI) and Symptom Severity Index (SSI): Rt upper arm</t>
+  </si>
+  <si>
+    <t>lt_upper_arm</t>
+  </si>
+  <si>
+    <t>Lt upper arm</t>
+  </si>
+  <si>
+    <t>Widespread Pain Index (WPI) and Symptom Severity Index (SSI): Lt upper arm</t>
+  </si>
+  <si>
+    <t>1=Yes|0=No</t>
   </si>
 </sst>
 </file>
@@ -1106,14 +1418,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B4F619F0-927D-42BE-B802-34E76A1D5A02}">
-  <dimension ref="A1:AD15"/>
+  <dimension ref="A1:AC47"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="2" max="2" width="33.19921875" customWidth="1"/>
-    <col min="3" max="3" width="18" customWidth="1"/>
+    <col min="1" max="1" width="33.19921875" customWidth="1"/>
+    <col min="2" max="2" width="18" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:30" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1201,360 +1513,859 @@
       <c r="AC1" t="s">
         <v>28</v>
       </c>
-      <c r="AD1" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="2" spans="1:30" x14ac:dyDescent="0.45">
+    </row>
+    <row r="2" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
+        <v>31</v>
+      </c>
+      <c r="B2" t="s">
+        <v>34</v>
+      </c>
+      <c r="C2" t="s">
+        <v>35</v>
+      </c>
+      <c r="D2" t="s">
+        <v>35</v>
+      </c>
+      <c r="E2" t="s">
         <v>30</v>
       </c>
-      <c r="B2" t="s">
+    </row>
+    <row r="3" spans="1:29" x14ac:dyDescent="0.45">
+      <c r="A3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B3" t="s">
+        <v>36</v>
+      </c>
+      <c r="C3" t="s">
+        <v>37</v>
+      </c>
+      <c r="D3" t="s">
+        <v>37</v>
+      </c>
+      <c r="E3" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="4" spans="1:29" x14ac:dyDescent="0.45">
+      <c r="A4" t="s">
+        <v>31</v>
+      </c>
+      <c r="B4" t="s">
+        <v>32</v>
+      </c>
+      <c r="C4" t="s">
         <v>33</v>
       </c>
-      <c r="C2" t="s">
-        <v>36</v>
-      </c>
-      <c r="D2" t="s">
-        <v>37</v>
-      </c>
-      <c r="E2" t="s">
-        <v>37</v>
-      </c>
-      <c r="F2" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="3" spans="1:30" x14ac:dyDescent="0.45">
-      <c r="A3" t="s">
+      <c r="D4" t="s">
+        <v>33</v>
+      </c>
+      <c r="E4" t="s">
         <v>30</v>
       </c>
-      <c r="B3" t="s">
-        <v>33</v>
-      </c>
-      <c r="C3" t="s">
-        <v>38</v>
-      </c>
-      <c r="D3" t="s">
-        <v>39</v>
-      </c>
-      <c r="E3" t="s">
-        <v>39</v>
-      </c>
-      <c r="F3" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="4" spans="1:30" x14ac:dyDescent="0.45">
-      <c r="A4" t="s">
-        <v>30</v>
-      </c>
-      <c r="B4" t="s">
-        <v>33</v>
-      </c>
-      <c r="C4" t="s">
-        <v>34</v>
-      </c>
-      <c r="D4" t="s">
-        <v>35</v>
-      </c>
-      <c r="E4" t="s">
-        <v>35</v>
-      </c>
-      <c r="F4" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="5" spans="1:30" x14ac:dyDescent="0.45">
+    </row>
+    <row r="5" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
-        <v>30</v>
+        <v>53</v>
       </c>
       <c r="B5" t="s">
         <v>55</v>
       </c>
       <c r="C5" t="s">
+        <v>42</v>
+      </c>
+      <c r="D5" t="s">
+        <v>42</v>
+      </c>
+      <c r="E5" t="s">
+        <v>29</v>
+      </c>
+      <c r="I5" t="s">
+        <v>38</v>
+      </c>
+      <c r="M5" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="6" spans="1:29" x14ac:dyDescent="0.45">
+      <c r="A6" t="s">
+        <v>53</v>
+      </c>
+      <c r="B6" t="s">
+        <v>56</v>
+      </c>
+      <c r="C6" t="s">
+        <v>43</v>
+      </c>
+      <c r="D6" t="s">
+        <v>43</v>
+      </c>
+      <c r="E6" t="s">
+        <v>29</v>
+      </c>
+      <c r="I6" t="s">
+        <v>38</v>
+      </c>
+      <c r="M6" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="7" spans="1:29" x14ac:dyDescent="0.45">
+      <c r="A7" t="s">
+        <v>53</v>
+      </c>
+      <c r="B7" t="s">
         <v>57</v>
       </c>
-      <c r="D5" t="s">
+      <c r="C7" t="s">
+        <v>41</v>
+      </c>
+      <c r="D7" t="s">
+        <v>41</v>
+      </c>
+      <c r="E7" t="s">
+        <v>29</v>
+      </c>
+      <c r="I7" t="s">
+        <v>38</v>
+      </c>
+      <c r="M7" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="8" spans="1:29" x14ac:dyDescent="0.45">
+      <c r="A8" t="s">
+        <v>53</v>
+      </c>
+      <c r="B8" t="s">
+        <v>58</v>
+      </c>
+      <c r="C8" t="s">
+        <v>39</v>
+      </c>
+      <c r="D8" t="s">
+        <v>39</v>
+      </c>
+      <c r="E8" t="s">
+        <v>29</v>
+      </c>
+      <c r="I8" t="s">
+        <v>38</v>
+      </c>
+      <c r="M8" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="9" spans="1:29" x14ac:dyDescent="0.45">
+      <c r="A9" t="s">
+        <v>54</v>
+      </c>
+      <c r="B9" t="s">
+        <v>59</v>
+      </c>
+      <c r="C9" t="s">
         <v>44</v>
       </c>
-      <c r="E5" t="s">
+      <c r="D9" t="s">
         <v>44</v>
       </c>
-      <c r="F5" t="s">
-        <v>31</v>
-      </c>
-      <c r="J5" t="s">
-        <v>40</v>
-      </c>
-      <c r="N5" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="6" spans="1:30" x14ac:dyDescent="0.45">
-      <c r="A6" t="s">
-        <v>30</v>
-      </c>
-      <c r="B6" t="s">
-        <v>55</v>
-      </c>
-      <c r="C6" t="s">
-        <v>58</v>
-      </c>
-      <c r="D6" t="s">
+      <c r="E9" t="s">
+        <v>29</v>
+      </c>
+      <c r="I9" t="s">
         <v>45</v>
       </c>
-      <c r="E6" t="s">
+      <c r="M9" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="10" spans="1:29" x14ac:dyDescent="0.45">
+      <c r="A10" t="s">
+        <v>54</v>
+      </c>
+      <c r="B10" t="s">
+        <v>60</v>
+      </c>
+      <c r="C10" t="s">
+        <v>47</v>
+      </c>
+      <c r="D10" t="s">
+        <v>47</v>
+      </c>
+      <c r="E10" t="s">
+        <v>29</v>
+      </c>
+      <c r="I10" t="s">
         <v>45</v>
       </c>
-      <c r="F6" t="s">
-        <v>31</v>
-      </c>
-      <c r="J6" t="s">
-        <v>40</v>
-      </c>
-      <c r="N6" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="7" spans="1:30" x14ac:dyDescent="0.45">
-      <c r="A7" t="s">
-        <v>30</v>
-      </c>
-      <c r="B7" t="s">
-        <v>55</v>
-      </c>
-      <c r="C7" t="s">
-        <v>59</v>
-      </c>
-      <c r="D7" t="s">
-        <v>43</v>
-      </c>
-      <c r="E7" t="s">
-        <v>43</v>
-      </c>
-      <c r="F7" t="s">
-        <v>31</v>
-      </c>
-      <c r="J7" t="s">
-        <v>40</v>
-      </c>
-      <c r="N7" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="8" spans="1:30" x14ac:dyDescent="0.45">
-      <c r="A8" t="s">
-        <v>30</v>
-      </c>
-      <c r="B8" t="s">
-        <v>55</v>
-      </c>
-      <c r="C8" t="s">
-        <v>60</v>
-      </c>
-      <c r="D8" t="s">
-        <v>41</v>
-      </c>
-      <c r="E8" t="s">
-        <v>41</v>
-      </c>
-      <c r="F8" t="s">
-        <v>31</v>
-      </c>
-      <c r="J8" t="s">
-        <v>40</v>
-      </c>
-      <c r="N8" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="9" spans="1:30" x14ac:dyDescent="0.45">
-      <c r="A9" t="s">
-        <v>30</v>
-      </c>
-      <c r="B9" t="s">
-        <v>56</v>
-      </c>
-      <c r="C9" t="s">
+      <c r="M10" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="11" spans="1:29" x14ac:dyDescent="0.45">
+      <c r="A11" t="s">
+        <v>54</v>
+      </c>
+      <c r="B11" t="s">
         <v>61</v>
       </c>
-      <c r="D9" t="s">
+      <c r="C11" t="s">
+        <v>51</v>
+      </c>
+      <c r="D11" t="s">
+        <v>51</v>
+      </c>
+      <c r="E11" t="s">
+        <v>29</v>
+      </c>
+      <c r="I11" t="s">
+        <v>45</v>
+      </c>
+      <c r="M11" t="s">
         <v>46</v>
       </c>
-      <c r="E9" t="s">
+    </row>
+    <row r="12" spans="1:29" x14ac:dyDescent="0.45">
+      <c r="A12" t="s">
+        <v>54</v>
+      </c>
+      <c r="B12" t="s">
+        <v>62</v>
+      </c>
+      <c r="C12" t="s">
+        <v>52</v>
+      </c>
+      <c r="D12" t="s">
+        <v>52</v>
+      </c>
+      <c r="E12" t="s">
+        <v>29</v>
+      </c>
+      <c r="I12" t="s">
+        <v>45</v>
+      </c>
+      <c r="M12" t="s">
         <v>46</v>
       </c>
-      <c r="F9" t="s">
-        <v>31</v>
-      </c>
-      <c r="J9" t="s">
-        <v>47</v>
-      </c>
-      <c r="N9" t="s">
+    </row>
+    <row r="13" spans="1:29" x14ac:dyDescent="0.45">
+      <c r="A13" t="s">
+        <v>54</v>
+      </c>
+      <c r="B13" t="s">
+        <v>63</v>
+      </c>
+      <c r="C13" t="s">
+        <v>50</v>
+      </c>
+      <c r="D13" t="s">
+        <v>50</v>
+      </c>
+      <c r="E13" t="s">
+        <v>29</v>
+      </c>
+      <c r="I13" t="s">
+        <v>45</v>
+      </c>
+      <c r="M13" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="14" spans="1:29" x14ac:dyDescent="0.45">
+      <c r="A14" t="s">
+        <v>54</v>
+      </c>
+      <c r="B14" t="s">
+        <v>64</v>
+      </c>
+      <c r="C14" t="s">
+        <v>49</v>
+      </c>
+      <c r="D14" t="s">
+        <v>49</v>
+      </c>
+      <c r="E14" t="s">
+        <v>29</v>
+      </c>
+      <c r="I14" t="s">
+        <v>45</v>
+      </c>
+      <c r="M14" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="15" spans="1:29" x14ac:dyDescent="0.45">
+      <c r="A15" t="s">
+        <v>54</v>
+      </c>
+      <c r="B15" t="s">
+        <v>65</v>
+      </c>
+      <c r="C15" t="s">
         <v>48</v>
       </c>
-    </row>
-    <row r="10" spans="1:30" x14ac:dyDescent="0.45">
-      <c r="A10" t="s">
-        <v>30</v>
-      </c>
-      <c r="B10" t="s">
-        <v>56</v>
-      </c>
-      <c r="C10" t="s">
-        <v>62</v>
-      </c>
-      <c r="D10" t="s">
-        <v>49</v>
-      </c>
-      <c r="E10" t="s">
-        <v>49</v>
-      </c>
-      <c r="F10" t="s">
-        <v>31</v>
-      </c>
-      <c r="J10" t="s">
-        <v>47</v>
-      </c>
-      <c r="N10" t="s">
+      <c r="D15" t="s">
         <v>48</v>
       </c>
-    </row>
-    <row r="11" spans="1:30" x14ac:dyDescent="0.45">
-      <c r="A11" t="s">
-        <v>30</v>
-      </c>
-      <c r="B11" t="s">
-        <v>56</v>
-      </c>
-      <c r="C11" t="s">
-        <v>63</v>
-      </c>
-      <c r="D11" t="s">
-        <v>53</v>
-      </c>
-      <c r="E11" t="s">
-        <v>53</v>
-      </c>
-      <c r="F11" t="s">
-        <v>31</v>
-      </c>
-      <c r="J11" t="s">
-        <v>47</v>
-      </c>
-      <c r="N11" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="12" spans="1:30" x14ac:dyDescent="0.45">
-      <c r="A12" t="s">
-        <v>30</v>
-      </c>
-      <c r="B12" t="s">
-        <v>56</v>
-      </c>
-      <c r="C12" t="s">
-        <v>64</v>
-      </c>
-      <c r="D12" t="s">
-        <v>54</v>
-      </c>
-      <c r="E12" t="s">
-        <v>54</v>
-      </c>
-      <c r="F12" t="s">
-        <v>31</v>
-      </c>
-      <c r="J12" t="s">
-        <v>47</v>
-      </c>
-      <c r="N12" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="13" spans="1:30" x14ac:dyDescent="0.45">
-      <c r="A13" t="s">
-        <v>30</v>
-      </c>
-      <c r="B13" t="s">
-        <v>56</v>
-      </c>
-      <c r="C13" t="s">
-        <v>65</v>
-      </c>
-      <c r="D13" t="s">
-        <v>52</v>
-      </c>
-      <c r="E13" t="s">
-        <v>52</v>
-      </c>
-      <c r="F13" t="s">
-        <v>31</v>
-      </c>
-      <c r="J13" t="s">
-        <v>47</v>
-      </c>
-      <c r="N13" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="14" spans="1:30" x14ac:dyDescent="0.45">
-      <c r="A14" t="s">
-        <v>30</v>
-      </c>
-      <c r="B14" t="s">
-        <v>56</v>
-      </c>
-      <c r="C14" t="s">
+      <c r="E15" t="s">
+        <v>29</v>
+      </c>
+      <c r="I15" t="s">
+        <v>45</v>
+      </c>
+      <c r="M15" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="16" spans="1:29" x14ac:dyDescent="0.45">
+      <c r="A16" t="s">
         <v>66</v>
       </c>
-      <c r="D14" t="s">
-        <v>51</v>
-      </c>
-      <c r="E14" t="s">
-        <v>51</v>
-      </c>
-      <c r="F14" t="s">
-        <v>31</v>
-      </c>
-      <c r="J14" t="s">
-        <v>47</v>
-      </c>
-      <c r="N14" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="15" spans="1:30" x14ac:dyDescent="0.45">
-      <c r="A15" t="s">
-        <v>30</v>
-      </c>
-      <c r="B15" t="s">
-        <v>56</v>
-      </c>
-      <c r="C15" t="s">
+      <c r="B16" t="s">
         <v>67</v>
       </c>
-      <c r="D15" t="s">
-        <v>50</v>
-      </c>
-      <c r="E15" t="s">
-        <v>50</v>
-      </c>
-      <c r="F15" t="s">
-        <v>31</v>
-      </c>
-      <c r="J15" t="s">
-        <v>47</v>
-      </c>
-      <c r="N15" t="s">
-        <v>48</v>
+      <c r="D16" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="A17" t="s">
+        <v>66</v>
+      </c>
+      <c r="B17" t="s">
+        <v>68</v>
+      </c>
+      <c r="D17" t="s">
+        <v>76</v>
+      </c>
+      <c r="M17" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="A18" t="s">
+        <v>66</v>
+      </c>
+      <c r="B18" t="s">
+        <v>69</v>
+      </c>
+      <c r="D18" t="s">
+        <v>77</v>
+      </c>
+      <c r="M18" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="19" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="A19" t="s">
+        <v>66</v>
+      </c>
+      <c r="B19" t="s">
+        <v>70</v>
+      </c>
+      <c r="D19" t="s">
+        <v>78</v>
+      </c>
+      <c r="M19" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="20" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="A20" t="s">
+        <v>66</v>
+      </c>
+      <c r="B20" t="s">
+        <v>71</v>
+      </c>
+      <c r="D20" t="s">
+        <v>79</v>
+      </c>
+      <c r="M20" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="21" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="A21" t="s">
+        <v>66</v>
+      </c>
+      <c r="B21" t="s">
+        <v>72</v>
+      </c>
+      <c r="D21" t="s">
+        <v>80</v>
+      </c>
+      <c r="M21" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="22" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="A22" t="s">
+        <v>66</v>
+      </c>
+      <c r="B22" t="s">
+        <v>73</v>
+      </c>
+      <c r="D22" t="s">
+        <v>81</v>
+      </c>
+      <c r="M22" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="23" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="A23" t="s">
+        <v>66</v>
+      </c>
+      <c r="B23" t="s">
+        <v>74</v>
+      </c>
+      <c r="D23" t="s">
+        <v>82</v>
+      </c>
+      <c r="M23" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="24" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="A24" t="s">
+        <v>103</v>
+      </c>
+      <c r="B24" t="s">
+        <v>86</v>
+      </c>
+      <c r="C24" t="s">
+        <v>104</v>
+      </c>
+      <c r="D24" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="25" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="A25" t="s">
+        <v>103</v>
+      </c>
+      <c r="B25" t="s">
+        <v>87</v>
+      </c>
+      <c r="C25" t="s">
+        <v>105</v>
+      </c>
+      <c r="D25" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="26" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="A26" t="s">
+        <v>103</v>
+      </c>
+      <c r="B26" t="s">
+        <v>88</v>
+      </c>
+      <c r="C26" t="s">
+        <v>106</v>
+      </c>
+      <c r="D26" t="s">
+        <v>123</v>
+      </c>
+      <c r="I26" t="s">
+        <v>138</v>
+      </c>
+      <c r="M26" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="27" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="A27" t="s">
+        <v>103</v>
+      </c>
+      <c r="B27" t="s">
+        <v>89</v>
+      </c>
+      <c r="C27" t="s">
+        <v>107</v>
+      </c>
+      <c r="D27" t="s">
+        <v>124</v>
+      </c>
+      <c r="I27" t="s">
+        <v>138</v>
+      </c>
+      <c r="M27" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="28" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="A28" t="s">
+        <v>103</v>
+      </c>
+      <c r="B28" t="s">
+        <v>90</v>
+      </c>
+      <c r="C28" t="s">
+        <v>108</v>
+      </c>
+      <c r="D28" t="s">
+        <v>125</v>
+      </c>
+      <c r="I28" t="s">
+        <v>138</v>
+      </c>
+      <c r="M28" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="29" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="A29" t="s">
+        <v>103</v>
+      </c>
+      <c r="B29" t="s">
+        <v>91</v>
+      </c>
+      <c r="C29" t="s">
+        <v>109</v>
+      </c>
+      <c r="D29" t="s">
+        <v>126</v>
+      </c>
+      <c r="I29" t="s">
+        <v>139</v>
+      </c>
+      <c r="M29" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="30" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="A30" t="s">
+        <v>103</v>
+      </c>
+      <c r="B30" t="s">
+        <v>92</v>
+      </c>
+      <c r="C30" t="s">
+        <v>110</v>
+      </c>
+      <c r="D30" t="s">
+        <v>127</v>
+      </c>
+      <c r="I30" t="s">
+        <v>139</v>
+      </c>
+      <c r="M30" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="31" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="A31" t="s">
+        <v>103</v>
+      </c>
+      <c r="B31" t="s">
+        <v>93</v>
+      </c>
+      <c r="C31" t="s">
+        <v>111</v>
+      </c>
+      <c r="D31" t="s">
+        <v>128</v>
+      </c>
+      <c r="I31" t="s">
+        <v>139</v>
+      </c>
+      <c r="M31" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="32" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="A32" t="s">
+        <v>103</v>
+      </c>
+      <c r="B32" t="s">
+        <v>94</v>
+      </c>
+      <c r="C32" t="s">
+        <v>112</v>
+      </c>
+      <c r="D32" t="s">
+        <v>129</v>
+      </c>
+      <c r="I32" t="s">
+        <v>139</v>
+      </c>
+      <c r="M32" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="33" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="A33" t="s">
+        <v>103</v>
+      </c>
+      <c r="B33" t="s">
+        <v>95</v>
+      </c>
+      <c r="C33" t="s">
+        <v>113</v>
+      </c>
+      <c r="D33" t="s">
+        <v>130</v>
+      </c>
+      <c r="I33" t="s">
+        <v>139</v>
+      </c>
+      <c r="M33" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="34" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="A34" t="s">
+        <v>103</v>
+      </c>
+      <c r="B34" t="s">
+        <v>96</v>
+      </c>
+      <c r="C34" t="s">
+        <v>114</v>
+      </c>
+      <c r="D34" t="s">
+        <v>131</v>
+      </c>
+      <c r="I34" t="s">
+        <v>139</v>
+      </c>
+      <c r="M34" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="35" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="A35" t="s">
+        <v>103</v>
+      </c>
+      <c r="B35" t="s">
+        <v>97</v>
+      </c>
+      <c r="C35" t="s">
+        <v>115</v>
+      </c>
+      <c r="D35" t="s">
+        <v>132</v>
+      </c>
+      <c r="I35" t="s">
+        <v>139</v>
+      </c>
+      <c r="M35" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="36" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="A36" t="s">
+        <v>103</v>
+      </c>
+      <c r="B36" t="s">
+        <v>98</v>
+      </c>
+      <c r="C36" t="s">
+        <v>116</v>
+      </c>
+      <c r="D36" t="s">
+        <v>133</v>
+      </c>
+      <c r="I36" t="s">
+        <v>140</v>
+      </c>
+      <c r="M36" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="37" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="A37" t="s">
+        <v>103</v>
+      </c>
+      <c r="B37" t="s">
+        <v>99</v>
+      </c>
+      <c r="C37" t="s">
+        <v>117</v>
+      </c>
+      <c r="D37" t="s">
+        <v>134</v>
+      </c>
+      <c r="I37" t="s">
+        <v>138</v>
+      </c>
+      <c r="M37" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="38" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="A38" t="s">
+        <v>103</v>
+      </c>
+      <c r="B38" t="s">
+        <v>100</v>
+      </c>
+      <c r="C38" t="s">
+        <v>118</v>
+      </c>
+      <c r="D38" t="s">
+        <v>135</v>
+      </c>
+      <c r="I38" t="s">
+        <v>141</v>
+      </c>
+      <c r="M38" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="39" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="A39" t="s">
+        <v>103</v>
+      </c>
+      <c r="B39" t="s">
+        <v>101</v>
+      </c>
+      <c r="C39" t="s">
+        <v>119</v>
+      </c>
+      <c r="D39" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="40" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="A40" t="s">
+        <v>103</v>
+      </c>
+      <c r="B40" t="s">
+        <v>102</v>
+      </c>
+      <c r="C40" t="s">
+        <v>120</v>
+      </c>
+      <c r="D40" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="41" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="A41" t="s">
+        <v>149</v>
+      </c>
+      <c r="B41" t="s">
+        <v>150</v>
+      </c>
+      <c r="C41" t="s">
+        <v>151</v>
+      </c>
+      <c r="D41" t="s">
+        <v>152</v>
+      </c>
+      <c r="M41" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="42" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="A42" t="s">
+        <v>149</v>
+      </c>
+      <c r="B42" t="s">
+        <v>153</v>
+      </c>
+      <c r="C42" t="s">
+        <v>154</v>
+      </c>
+      <c r="D42" t="s">
+        <v>155</v>
+      </c>
+      <c r="M42" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="43" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="A43" t="s">
+        <v>149</v>
+      </c>
+      <c r="B43" t="s">
+        <v>156</v>
+      </c>
+      <c r="C43" t="s">
+        <v>157</v>
+      </c>
+      <c r="D43" t="s">
+        <v>158</v>
+      </c>
+      <c r="M43" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="44" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="A44" t="s">
+        <v>149</v>
+      </c>
+      <c r="B44" t="s">
+        <v>159</v>
+      </c>
+      <c r="C44" t="s">
+        <v>160</v>
+      </c>
+      <c r="D44" t="s">
+        <v>161</v>
+      </c>
+      <c r="M44" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="45" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="A45" t="s">
+        <v>149</v>
+      </c>
+      <c r="B45" t="s">
+        <v>162</v>
+      </c>
+      <c r="C45" t="s">
+        <v>163</v>
+      </c>
+      <c r="D45" t="s">
+        <v>164</v>
+      </c>
+      <c r="M45" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="46" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="A46" t="s">
+        <v>149</v>
+      </c>
+      <c r="B46" t="s">
+        <v>165</v>
+      </c>
+      <c r="C46" t="s">
+        <v>166</v>
+      </c>
+      <c r="D46" t="s">
+        <v>167</v>
+      </c>
+      <c r="M46" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="47" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="A47" t="s">
+        <v>149</v>
+      </c>
+      <c r="B47" t="s">
+        <v>168</v>
+      </c>
+      <c r="C47" t="s">
+        <v>169</v>
+      </c>
+      <c r="D47" t="s">
+        <v>170</v>
+      </c>
+      <c r="M47" t="s">
+        <v>171</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AD15" xr:uid="{B4F619F0-927D-42BE-B802-34E76A1D5A02}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:AD15">
-      <sortCondition ref="B1:B15"/>
+  <autoFilter ref="A1:AC15" xr:uid="{B4F619F0-927D-42BE-B802-34E76A1D5A02}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:AC15">
+      <sortCondition ref="A1:A15"/>
     </sortState>
   </autoFilter>
   <phoneticPr fontId="18" type="noConversion"/>

--- a/CDE_ID_detective_revamp/in/Testfile.xlsx
+++ b/CDE_ID_detective_revamp/in/Testfile.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lmaefos\Code Stuffs\CDE_detective\CDE_ID_detective_revamp\in\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{817B149D-0F69-43F3-8A18-7056A50B2854}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B1A64F1D-8F3C-4056-850A-EC6EC69AC4AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-19305" yWindow="4500" windowWidth="19410" windowHeight="20985" xr2:uid="{B4172F7E-1829-43FF-A6F3-7109D1C548C2}"/>
+    <workbookView xWindow="-36585" yWindow="7755" windowWidth="25830" windowHeight="15105" xr2:uid="{B4172F7E-1829-43FF-A6F3-7109D1C548C2}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -1421,8 +1421,35 @@
   <dimension ref="A1:AC47"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="33.19921875" customWidth="1"/>
-    <col min="2" max="2" width="18" customWidth="1"/>
+    <col min="1" max="1" width="30.73046875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="19.265625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="6" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.796875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="6.265625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="8.1328125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="18.9296875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="21" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="16.86328125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="18.06640625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="20.265625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="20" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="12.46484375" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="13.73046875" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.19921875" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="11.265625" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="11.86328125" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="8.86328125" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="32.3984375" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="35.73046875" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="33.3984375" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="31.796875" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="27.265625" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="30.53125" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="26.59765625" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="20.73046875" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="21.73046875" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="24.06640625" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="20.1328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:29" x14ac:dyDescent="0.45">
